--- a/activitereelford.xlsx
+++ b/activitereelford.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\OneDrive\Bureau\CODE HTML\Developpements\APP KENT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\OneDrive\Bureau\CODE HTML\Developpements\APP KENT VERCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8149121-90E2-4B62-8A06-4CA20BB0C0C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{542FBBE8-0032-492C-ABFF-5DD4EE2964D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1741" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2929" uniqueCount="498">
   <si>
     <t>N°commande</t>
   </si>
@@ -1039,6 +1039,498 @@
   </si>
   <si>
     <t>Janvier</t>
+  </si>
+  <si>
+    <t>Mars</t>
+  </si>
+  <si>
+    <t>26405911</t>
+  </si>
+  <si>
+    <t>26606320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85626 00                 </t>
+  </si>
+  <si>
+    <t>85626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARBON KIT                                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE GGE FEUILLET         </t>
+  </si>
+  <si>
+    <t>26405913</t>
+  </si>
+  <si>
+    <t>26606321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87052 10                 </t>
+  </si>
+  <si>
+    <t>87052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULTRAFILL 3 GREY(GRIS)   500ML UFL3-G - AEROSOL 500 ML       </t>
+  </si>
+  <si>
+    <t>26406213</t>
+  </si>
+  <si>
+    <t>26606575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83878 10                 </t>
+  </si>
+  <si>
+    <t>83878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NETTOYANT CUIR NATUREL                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE DH AUTOMOBILES       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86473 22                 </t>
+  </si>
+  <si>
+    <t>86473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESODORISANT FRAICHEUR COTON                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86877 10                 </t>
+  </si>
+  <si>
+    <t>86877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERFORMANCE NLR BOUT 1L                                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1341 33                 </t>
+  </si>
+  <si>
+    <t>A1341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISQUES DURALITE 75MM P500 50/PK                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1343 22                 </t>
+  </si>
+  <si>
+    <t>A1343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISQUES DURALITE 75MM P800 50 PAR BOITE                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1471 00                 </t>
+  </si>
+  <si>
+    <t>A1471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINECUT 1000 77 MM (VIOLET)                                  </t>
+  </si>
+  <si>
+    <t>26406304</t>
+  </si>
+  <si>
+    <t>26606592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86335 10                 </t>
+  </si>
+  <si>
+    <t>86335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APPRET D'IMPRESSION SPOT PRIMER GRIS 400ML                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86336 10                 </t>
+  </si>
+  <si>
+    <t>86336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APPRET D'IMPRESSION SPOT PRIMER BLANC 400ML                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86916 22                 </t>
+  </si>
+  <si>
+    <t>86916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROSEAL 303 JOINT PULVE BLANC                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">87051 10                 </t>
+  </si>
+  <si>
+    <t>87051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULTRAFILL 3 BLACK(NOIR)  500ML UFL3-BLK - AEROSOL 500 ML     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">87070 02                 </t>
+  </si>
+  <si>
+    <t>87070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT SUPER BOND                                               </t>
+  </si>
+  <si>
+    <t>26406352</t>
+  </si>
+  <si>
+    <t>26606721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85107 22                 </t>
+  </si>
+  <si>
+    <t>85107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT COLLE PU UREFIX 60 CART.                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE MECA GERMAIN         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">87177 22                 </t>
+  </si>
+  <si>
+    <t>87177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POWER WIPES+ 70/PK                                           </t>
+  </si>
+  <si>
+    <t>26406355</t>
+  </si>
+  <si>
+    <t>26606723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86214 28                 </t>
+  </si>
+  <si>
+    <t>86214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PANEL DEGREASER 5L                                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE CARROSSERIE ALEXIS   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">87107 22                 </t>
+  </si>
+  <si>
+    <t>87107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HST BLACK 16MMx15M RUBAN ADHESIF NOIR 16MM                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">87139 22                 </t>
+  </si>
+  <si>
+    <t>87139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILM DE RENFORT PLASTIQUE 13CM ROUL 3,6M                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">87214 00                 </t>
+  </si>
+  <si>
+    <t>87214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PULVERISATEUR A POMPE - RESISTANT AUX SOLVANTS               </t>
+  </si>
+  <si>
+    <t>26406515</t>
+  </si>
+  <si>
+    <t>26606884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84335 27                 </t>
+  </si>
+  <si>
+    <t>84335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT 1 GRAISSE C1200 PRESSURE PACK + 1 BROSSE APPLICATEUR     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE GGE GOULAIN          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86680 22                 </t>
+  </si>
+  <si>
+    <t>86680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTI TAPE EVO - 50 MM X 50 M                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86847 22                 </t>
+  </si>
+  <si>
+    <t>86847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRAISSE BLEU 1L - POT 1KG                                    </t>
+  </si>
+  <si>
+    <t>26406516</t>
+  </si>
+  <si>
+    <t>26607029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86791 28                 </t>
+  </si>
+  <si>
+    <t>86791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAPID BOND SE BLANC/AMBRE 7MN                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">87255 02                 </t>
+  </si>
+  <si>
+    <t>87255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT UPHOLSTERY CLEANER                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C0002 24                 </t>
+  </si>
+  <si>
+    <t>C0002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OVEN CLEANER - NETT DEPOTS CAR BONE ET RESIDUS BRULES        </t>
+  </si>
+  <si>
+    <t>26406517</t>
+  </si>
+  <si>
+    <t>26606885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86539 16                 </t>
+  </si>
+  <si>
+    <t>86539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUTLOCK BLEU 50ML                                            </t>
+  </si>
+  <si>
+    <t>26406799</t>
+  </si>
+  <si>
+    <t>26607181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86637 22                 </t>
+  </si>
+  <si>
+    <t>86637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPRAY WAX 500ML                                              </t>
+  </si>
+  <si>
+    <t>26407068</t>
+  </si>
+  <si>
+    <t>26607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE CARR KEVIN           </t>
+  </si>
+  <si>
+    <t>26407108</t>
+  </si>
+  <si>
+    <t>26607526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86605 10                 </t>
+  </si>
+  <si>
+    <t>86605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERFORMANCE ABRASIVE 2                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE ERIC                 </t>
+  </si>
+  <si>
+    <t>26407349</t>
+  </si>
+  <si>
+    <t>26607693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86727 10                 </t>
+  </si>
+  <si>
+    <t>86727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WHITE GREASE III ES AER 500ML (BUSE EASY STRAW)              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">87436 24                 </t>
+  </si>
+  <si>
+    <t>87436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIR CO ONE SHOT 150ML ACOS 150ML                             </t>
+  </si>
+  <si>
+    <t>26407479</t>
+  </si>
+  <si>
+    <t>26607933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87053 10                 </t>
+  </si>
+  <si>
+    <t>87053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULTRAFILL 3 WHITE(BLANC) 500ML UFL3-W - AEROSOL 500 ML       </t>
+  </si>
+  <si>
+    <t>26407618</t>
+  </si>
+  <si>
+    <t>26607974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30190 00                 </t>
+  </si>
+  <si>
+    <t>30190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PULVERISATEUR 600ml                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">85755 00                 </t>
+  </si>
+  <si>
+    <t>85755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPONGES MOUSSE PK DE 4                                       </t>
+  </si>
+  <si>
+    <t>26408237</t>
+  </si>
+  <si>
+    <t>26608898</t>
+  </si>
+  <si>
+    <t>26408688</t>
+  </si>
+  <si>
+    <t>26609376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE CARROSSERIE KEVIN    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">87722 22                 </t>
+  </si>
+  <si>
+    <t>87722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTI GRAVILLON TOUGHCOAT GRIS BOUT 1L                        </t>
+  </si>
+  <si>
+    <t>26408689</t>
+  </si>
+  <si>
+    <t>26609377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD ERIC HEBERT           </t>
+  </si>
+  <si>
+    <t>26406324</t>
+  </si>
+  <si>
+    <t>26606839</t>
+  </si>
+  <si>
+    <t>568316</t>
+  </si>
+  <si>
+    <t>CLAUDE FOURNIS AUTOMOBILES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87200 22                 </t>
+  </si>
+  <si>
+    <t>87200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PREMUIM CAR SHAMPOO 200 L                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE GERMAIN              </t>
+  </si>
+  <si>
+    <t>FBB</t>
+  </si>
+  <si>
+    <t>8 PLACE DE BOSTON</t>
+  </si>
+  <si>
+    <t>26406421</t>
+  </si>
+  <si>
+    <t>26606843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87203 00                 </t>
+  </si>
+  <si>
+    <t>87203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOSING PUMP SHAMPOO                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26406324                 </t>
   </si>
 </sst>
 </file>
@@ -1414,7 +1906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W96"/>
+  <dimension ref="A1:W162"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.1796875" bestFit="1" customWidth="1"/>
@@ -8257,6 +8749,4692 @@
         <v>333</v>
       </c>
     </row>
+    <row r="97" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>335</v>
+      </c>
+      <c r="B97" t="s">
+        <v>336</v>
+      </c>
+      <c r="C97" t="s">
+        <v>34</v>
+      </c>
+      <c r="D97" t="s">
+        <v>35</v>
+      </c>
+      <c r="E97" t="s">
+        <v>36</v>
+      </c>
+      <c r="F97" s="1">
+        <v>46083</v>
+      </c>
+      <c r="G97" t="s">
+        <v>337</v>
+      </c>
+      <c r="H97" t="s">
+        <v>338</v>
+      </c>
+      <c r="I97" t="s">
+        <v>339</v>
+      </c>
+      <c r="J97">
+        <v>1</v>
+      </c>
+      <c r="K97">
+        <v>90.9</v>
+      </c>
+      <c r="L97">
+        <v>90.9</v>
+      </c>
+      <c r="M97" t="s">
+        <v>22</v>
+      </c>
+      <c r="N97" t="s">
+        <v>23</v>
+      </c>
+      <c r="O97" s="1">
+        <v>46083</v>
+      </c>
+      <c r="P97" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>24</v>
+      </c>
+      <c r="R97" t="s">
+        <v>41</v>
+      </c>
+      <c r="S97" t="s">
+        <v>25</v>
+      </c>
+      <c r="T97" t="s">
+        <v>42</v>
+      </c>
+      <c r="U97" t="s">
+        <v>43</v>
+      </c>
+      <c r="V97" t="s">
+        <v>44</v>
+      </c>
+      <c r="W97" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>341</v>
+      </c>
+      <c r="B98" t="s">
+        <v>342</v>
+      </c>
+      <c r="C98" t="s">
+        <v>34</v>
+      </c>
+      <c r="D98" t="s">
+        <v>35</v>
+      </c>
+      <c r="E98" t="s">
+        <v>36</v>
+      </c>
+      <c r="F98" s="1">
+        <v>46083</v>
+      </c>
+      <c r="G98" t="s">
+        <v>108</v>
+      </c>
+      <c r="H98" t="s">
+        <v>109</v>
+      </c>
+      <c r="I98" t="s">
+        <v>110</v>
+      </c>
+      <c r="J98">
+        <v>1</v>
+      </c>
+      <c r="K98">
+        <v>20.11</v>
+      </c>
+      <c r="L98">
+        <v>20.11</v>
+      </c>
+      <c r="M98" t="s">
+        <v>22</v>
+      </c>
+      <c r="N98" t="s">
+        <v>23</v>
+      </c>
+      <c r="O98" s="1">
+        <v>46083</v>
+      </c>
+      <c r="P98" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>24</v>
+      </c>
+      <c r="R98" t="s">
+        <v>41</v>
+      </c>
+      <c r="S98" t="s">
+        <v>25</v>
+      </c>
+      <c r="T98" t="s">
+        <v>42</v>
+      </c>
+      <c r="U98" t="s">
+        <v>43</v>
+      </c>
+      <c r="V98" t="s">
+        <v>44</v>
+      </c>
+      <c r="W98" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>341</v>
+      </c>
+      <c r="B99" t="s">
+        <v>342</v>
+      </c>
+      <c r="C99" t="s">
+        <v>34</v>
+      </c>
+      <c r="D99" t="s">
+        <v>35</v>
+      </c>
+      <c r="E99" t="s">
+        <v>36</v>
+      </c>
+      <c r="F99" s="1">
+        <v>46083</v>
+      </c>
+      <c r="G99" t="s">
+        <v>343</v>
+      </c>
+      <c r="H99" t="s">
+        <v>344</v>
+      </c>
+      <c r="I99" t="s">
+        <v>345</v>
+      </c>
+      <c r="J99">
+        <v>1</v>
+      </c>
+      <c r="K99">
+        <v>13.12</v>
+      </c>
+      <c r="L99">
+        <v>13.12</v>
+      </c>
+      <c r="M99" t="s">
+        <v>22</v>
+      </c>
+      <c r="N99" t="s">
+        <v>23</v>
+      </c>
+      <c r="O99" s="1">
+        <v>46083</v>
+      </c>
+      <c r="P99" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>24</v>
+      </c>
+      <c r="R99" t="s">
+        <v>41</v>
+      </c>
+      <c r="S99" t="s">
+        <v>25</v>
+      </c>
+      <c r="T99" t="s">
+        <v>42</v>
+      </c>
+      <c r="U99" t="s">
+        <v>43</v>
+      </c>
+      <c r="V99" t="s">
+        <v>44</v>
+      </c>
+      <c r="W99" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>346</v>
+      </c>
+      <c r="B100" t="s">
+        <v>347</v>
+      </c>
+      <c r="C100" t="s">
+        <v>34</v>
+      </c>
+      <c r="D100" t="s">
+        <v>35</v>
+      </c>
+      <c r="E100" t="s">
+        <v>36</v>
+      </c>
+      <c r="F100" s="1">
+        <v>46085</v>
+      </c>
+      <c r="G100" t="s">
+        <v>348</v>
+      </c>
+      <c r="H100" t="s">
+        <v>349</v>
+      </c>
+      <c r="I100" t="s">
+        <v>350</v>
+      </c>
+      <c r="J100">
+        <v>1</v>
+      </c>
+      <c r="K100">
+        <v>33.69</v>
+      </c>
+      <c r="L100">
+        <v>33.69</v>
+      </c>
+      <c r="M100" t="s">
+        <v>22</v>
+      </c>
+      <c r="N100" t="s">
+        <v>23</v>
+      </c>
+      <c r="O100" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P100" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>24</v>
+      </c>
+      <c r="R100" t="s">
+        <v>41</v>
+      </c>
+      <c r="S100" t="s">
+        <v>25</v>
+      </c>
+      <c r="T100" t="s">
+        <v>42</v>
+      </c>
+      <c r="U100" t="s">
+        <v>43</v>
+      </c>
+      <c r="V100" t="s">
+        <v>44</v>
+      </c>
+      <c r="W100" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>346</v>
+      </c>
+      <c r="B101" t="s">
+        <v>347</v>
+      </c>
+      <c r="C101" t="s">
+        <v>34</v>
+      </c>
+      <c r="D101" t="s">
+        <v>35</v>
+      </c>
+      <c r="E101" t="s">
+        <v>36</v>
+      </c>
+      <c r="F101" s="1">
+        <v>46085</v>
+      </c>
+      <c r="G101" t="s">
+        <v>352</v>
+      </c>
+      <c r="H101" t="s">
+        <v>353</v>
+      </c>
+      <c r="I101" t="s">
+        <v>354</v>
+      </c>
+      <c r="J101">
+        <v>1</v>
+      </c>
+      <c r="K101">
+        <v>10.88</v>
+      </c>
+      <c r="L101">
+        <v>10.88</v>
+      </c>
+      <c r="M101" t="s">
+        <v>22</v>
+      </c>
+      <c r="N101" t="s">
+        <v>23</v>
+      </c>
+      <c r="O101" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P101" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>24</v>
+      </c>
+      <c r="R101" t="s">
+        <v>41</v>
+      </c>
+      <c r="S101" t="s">
+        <v>25</v>
+      </c>
+      <c r="T101" t="s">
+        <v>42</v>
+      </c>
+      <c r="U101" t="s">
+        <v>43</v>
+      </c>
+      <c r="V101" t="s">
+        <v>44</v>
+      </c>
+      <c r="W101" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>346</v>
+      </c>
+      <c r="B102" t="s">
+        <v>347</v>
+      </c>
+      <c r="C102" t="s">
+        <v>34</v>
+      </c>
+      <c r="D102" t="s">
+        <v>35</v>
+      </c>
+      <c r="E102" t="s">
+        <v>36</v>
+      </c>
+      <c r="F102" s="1">
+        <v>46085</v>
+      </c>
+      <c r="G102" t="s">
+        <v>355</v>
+      </c>
+      <c r="H102" t="s">
+        <v>356</v>
+      </c>
+      <c r="I102" t="s">
+        <v>357</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
+      </c>
+      <c r="K102">
+        <v>19.350000000000001</v>
+      </c>
+      <c r="L102">
+        <v>19.350000000000001</v>
+      </c>
+      <c r="M102" t="s">
+        <v>22</v>
+      </c>
+      <c r="N102" t="s">
+        <v>23</v>
+      </c>
+      <c r="O102" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P102" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>24</v>
+      </c>
+      <c r="R102" t="s">
+        <v>41</v>
+      </c>
+      <c r="S102" t="s">
+        <v>25</v>
+      </c>
+      <c r="T102" t="s">
+        <v>42</v>
+      </c>
+      <c r="U102" t="s">
+        <v>43</v>
+      </c>
+      <c r="V102" t="s">
+        <v>44</v>
+      </c>
+      <c r="W102" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>346</v>
+      </c>
+      <c r="B103" t="s">
+        <v>347</v>
+      </c>
+      <c r="C103" t="s">
+        <v>34</v>
+      </c>
+      <c r="D103" t="s">
+        <v>35</v>
+      </c>
+      <c r="E103" t="s">
+        <v>36</v>
+      </c>
+      <c r="F103" s="1">
+        <v>46085</v>
+      </c>
+      <c r="G103" t="s">
+        <v>358</v>
+      </c>
+      <c r="H103" t="s">
+        <v>359</v>
+      </c>
+      <c r="I103" t="s">
+        <v>360</v>
+      </c>
+      <c r="J103">
+        <v>1</v>
+      </c>
+      <c r="K103">
+        <v>7.62</v>
+      </c>
+      <c r="L103">
+        <v>7.62</v>
+      </c>
+      <c r="M103" t="s">
+        <v>22</v>
+      </c>
+      <c r="N103" t="s">
+        <v>23</v>
+      </c>
+      <c r="O103" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P103" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>24</v>
+      </c>
+      <c r="R103" t="s">
+        <v>41</v>
+      </c>
+      <c r="S103" t="s">
+        <v>25</v>
+      </c>
+      <c r="T103" t="s">
+        <v>42</v>
+      </c>
+      <c r="U103" t="s">
+        <v>43</v>
+      </c>
+      <c r="V103" t="s">
+        <v>44</v>
+      </c>
+      <c r="W103" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="104" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>346</v>
+      </c>
+      <c r="B104" t="s">
+        <v>347</v>
+      </c>
+      <c r="C104" t="s">
+        <v>34</v>
+      </c>
+      <c r="D104" t="s">
+        <v>35</v>
+      </c>
+      <c r="E104" t="s">
+        <v>36</v>
+      </c>
+      <c r="F104" s="1">
+        <v>46085</v>
+      </c>
+      <c r="G104" t="s">
+        <v>361</v>
+      </c>
+      <c r="H104" t="s">
+        <v>362</v>
+      </c>
+      <c r="I104" t="s">
+        <v>363</v>
+      </c>
+      <c r="J104">
+        <v>1</v>
+      </c>
+      <c r="K104">
+        <v>7.62</v>
+      </c>
+      <c r="L104">
+        <v>7.62</v>
+      </c>
+      <c r="M104" t="s">
+        <v>22</v>
+      </c>
+      <c r="N104" t="s">
+        <v>23</v>
+      </c>
+      <c r="O104" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P104" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>24</v>
+      </c>
+      <c r="R104" t="s">
+        <v>41</v>
+      </c>
+      <c r="S104" t="s">
+        <v>25</v>
+      </c>
+      <c r="T104" t="s">
+        <v>42</v>
+      </c>
+      <c r="U104" t="s">
+        <v>43</v>
+      </c>
+      <c r="V104" t="s">
+        <v>44</v>
+      </c>
+      <c r="W104" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="105" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>346</v>
+      </c>
+      <c r="B105" t="s">
+        <v>347</v>
+      </c>
+      <c r="C105" t="s">
+        <v>34</v>
+      </c>
+      <c r="D105" t="s">
+        <v>35</v>
+      </c>
+      <c r="E105" t="s">
+        <v>36</v>
+      </c>
+      <c r="F105" s="1">
+        <v>46085</v>
+      </c>
+      <c r="G105" t="s">
+        <v>364</v>
+      </c>
+      <c r="H105" t="s">
+        <v>365</v>
+      </c>
+      <c r="I105" t="s">
+        <v>366</v>
+      </c>
+      <c r="J105">
+        <v>1</v>
+      </c>
+      <c r="K105">
+        <v>13.29</v>
+      </c>
+      <c r="L105">
+        <v>13.29</v>
+      </c>
+      <c r="M105" t="s">
+        <v>22</v>
+      </c>
+      <c r="N105" t="s">
+        <v>23</v>
+      </c>
+      <c r="O105" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P105" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>24</v>
+      </c>
+      <c r="R105" t="s">
+        <v>41</v>
+      </c>
+      <c r="S105" t="s">
+        <v>25</v>
+      </c>
+      <c r="T105" t="s">
+        <v>42</v>
+      </c>
+      <c r="U105" t="s">
+        <v>43</v>
+      </c>
+      <c r="V105" t="s">
+        <v>44</v>
+      </c>
+      <c r="W105" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="106" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>346</v>
+      </c>
+      <c r="B106" t="s">
+        <v>347</v>
+      </c>
+      <c r="C106" t="s">
+        <v>34</v>
+      </c>
+      <c r="D106" t="s">
+        <v>35</v>
+      </c>
+      <c r="E106" t="s">
+        <v>36</v>
+      </c>
+      <c r="F106" s="1">
+        <v>46085</v>
+      </c>
+      <c r="G106" t="s">
+        <v>303</v>
+      </c>
+      <c r="H106" t="s">
+        <v>304</v>
+      </c>
+      <c r="I106" t="s">
+        <v>305</v>
+      </c>
+      <c r="J106">
+        <v>1</v>
+      </c>
+      <c r="K106">
+        <v>13.29</v>
+      </c>
+      <c r="L106">
+        <v>13.29</v>
+      </c>
+      <c r="M106" t="s">
+        <v>22</v>
+      </c>
+      <c r="N106" t="s">
+        <v>23</v>
+      </c>
+      <c r="O106" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P106" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>24</v>
+      </c>
+      <c r="R106" t="s">
+        <v>41</v>
+      </c>
+      <c r="S106" t="s">
+        <v>25</v>
+      </c>
+      <c r="T106" t="s">
+        <v>42</v>
+      </c>
+      <c r="U106" t="s">
+        <v>43</v>
+      </c>
+      <c r="V106" t="s">
+        <v>44</v>
+      </c>
+      <c r="W106" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>367</v>
+      </c>
+      <c r="B107" t="s">
+        <v>368</v>
+      </c>
+      <c r="C107" t="s">
+        <v>34</v>
+      </c>
+      <c r="D107" t="s">
+        <v>35</v>
+      </c>
+      <c r="E107" t="s">
+        <v>36</v>
+      </c>
+      <c r="F107" s="1">
+        <v>46085</v>
+      </c>
+      <c r="G107" t="s">
+        <v>37</v>
+      </c>
+      <c r="H107" t="s">
+        <v>38</v>
+      </c>
+      <c r="I107" t="s">
+        <v>39</v>
+      </c>
+      <c r="J107">
+        <v>2</v>
+      </c>
+      <c r="K107">
+        <v>17.63</v>
+      </c>
+      <c r="L107">
+        <v>35.26</v>
+      </c>
+      <c r="M107" t="s">
+        <v>22</v>
+      </c>
+      <c r="N107" t="s">
+        <v>23</v>
+      </c>
+      <c r="O107" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P107" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>24</v>
+      </c>
+      <c r="R107" t="s">
+        <v>41</v>
+      </c>
+      <c r="S107" t="s">
+        <v>25</v>
+      </c>
+      <c r="T107" t="s">
+        <v>42</v>
+      </c>
+      <c r="U107" t="s">
+        <v>43</v>
+      </c>
+      <c r="V107" t="s">
+        <v>44</v>
+      </c>
+      <c r="W107" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="108" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>367</v>
+      </c>
+      <c r="B108" t="s">
+        <v>368</v>
+      </c>
+      <c r="C108" t="s">
+        <v>34</v>
+      </c>
+      <c r="D108" t="s">
+        <v>35</v>
+      </c>
+      <c r="E108" t="s">
+        <v>36</v>
+      </c>
+      <c r="F108" s="1">
+        <v>46085</v>
+      </c>
+      <c r="G108" t="s">
+        <v>369</v>
+      </c>
+      <c r="H108" t="s">
+        <v>370</v>
+      </c>
+      <c r="I108" t="s">
+        <v>371</v>
+      </c>
+      <c r="J108">
+        <v>1</v>
+      </c>
+      <c r="K108">
+        <v>7.39</v>
+      </c>
+      <c r="L108">
+        <v>7.39</v>
+      </c>
+      <c r="M108" t="s">
+        <v>22</v>
+      </c>
+      <c r="N108" t="s">
+        <v>23</v>
+      </c>
+      <c r="O108" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P108" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>24</v>
+      </c>
+      <c r="R108" t="s">
+        <v>41</v>
+      </c>
+      <c r="S108" t="s">
+        <v>25</v>
+      </c>
+      <c r="T108" t="s">
+        <v>42</v>
+      </c>
+      <c r="U108" t="s">
+        <v>43</v>
+      </c>
+      <c r="V108" t="s">
+        <v>44</v>
+      </c>
+      <c r="W108" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="109" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>367</v>
+      </c>
+      <c r="B109" t="s">
+        <v>368</v>
+      </c>
+      <c r="C109" t="s">
+        <v>34</v>
+      </c>
+      <c r="D109" t="s">
+        <v>35</v>
+      </c>
+      <c r="E109" t="s">
+        <v>36</v>
+      </c>
+      <c r="F109" s="1">
+        <v>46085</v>
+      </c>
+      <c r="G109" t="s">
+        <v>372</v>
+      </c>
+      <c r="H109" t="s">
+        <v>373</v>
+      </c>
+      <c r="I109" t="s">
+        <v>374</v>
+      </c>
+      <c r="J109">
+        <v>1</v>
+      </c>
+      <c r="K109">
+        <v>7.39</v>
+      </c>
+      <c r="L109">
+        <v>7.39</v>
+      </c>
+      <c r="M109" t="s">
+        <v>22</v>
+      </c>
+      <c r="N109" t="s">
+        <v>23</v>
+      </c>
+      <c r="O109" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P109" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>24</v>
+      </c>
+      <c r="R109" t="s">
+        <v>41</v>
+      </c>
+      <c r="S109" t="s">
+        <v>25</v>
+      </c>
+      <c r="T109" t="s">
+        <v>42</v>
+      </c>
+      <c r="U109" t="s">
+        <v>43</v>
+      </c>
+      <c r="V109" t="s">
+        <v>44</v>
+      </c>
+      <c r="W109" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="110" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>367</v>
+      </c>
+      <c r="B110" t="s">
+        <v>368</v>
+      </c>
+      <c r="C110" t="s">
+        <v>34</v>
+      </c>
+      <c r="D110" t="s">
+        <v>35</v>
+      </c>
+      <c r="E110" t="s">
+        <v>36</v>
+      </c>
+      <c r="F110" s="1">
+        <v>46085</v>
+      </c>
+      <c r="G110" t="s">
+        <v>221</v>
+      </c>
+      <c r="H110" t="s">
+        <v>222</v>
+      </c>
+      <c r="I110" t="s">
+        <v>223</v>
+      </c>
+      <c r="J110">
+        <v>1</v>
+      </c>
+      <c r="K110">
+        <v>15.86</v>
+      </c>
+      <c r="L110">
+        <v>15.86</v>
+      </c>
+      <c r="M110" t="s">
+        <v>22</v>
+      </c>
+      <c r="N110" t="s">
+        <v>23</v>
+      </c>
+      <c r="O110" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P110" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>24</v>
+      </c>
+      <c r="R110" t="s">
+        <v>41</v>
+      </c>
+      <c r="S110" t="s">
+        <v>25</v>
+      </c>
+      <c r="T110" t="s">
+        <v>42</v>
+      </c>
+      <c r="U110" t="s">
+        <v>43</v>
+      </c>
+      <c r="V110" t="s">
+        <v>44</v>
+      </c>
+      <c r="W110" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="111" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>367</v>
+      </c>
+      <c r="B111" t="s">
+        <v>368</v>
+      </c>
+      <c r="C111" t="s">
+        <v>34</v>
+      </c>
+      <c r="D111" t="s">
+        <v>35</v>
+      </c>
+      <c r="E111" t="s">
+        <v>36</v>
+      </c>
+      <c r="F111" s="1">
+        <v>46085</v>
+      </c>
+      <c r="G111" t="s">
+        <v>69</v>
+      </c>
+      <c r="H111" t="s">
+        <v>70</v>
+      </c>
+      <c r="I111" t="s">
+        <v>71</v>
+      </c>
+      <c r="J111">
+        <v>1</v>
+      </c>
+      <c r="K111">
+        <v>10.59</v>
+      </c>
+      <c r="L111">
+        <v>10.59</v>
+      </c>
+      <c r="M111" t="s">
+        <v>22</v>
+      </c>
+      <c r="N111" t="s">
+        <v>23</v>
+      </c>
+      <c r="O111" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P111" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>24</v>
+      </c>
+      <c r="R111" t="s">
+        <v>41</v>
+      </c>
+      <c r="S111" t="s">
+        <v>25</v>
+      </c>
+      <c r="T111" t="s">
+        <v>42</v>
+      </c>
+      <c r="U111" t="s">
+        <v>43</v>
+      </c>
+      <c r="V111" t="s">
+        <v>44</v>
+      </c>
+      <c r="W111" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>367</v>
+      </c>
+      <c r="B112" t="s">
+        <v>368</v>
+      </c>
+      <c r="C112" t="s">
+        <v>34</v>
+      </c>
+      <c r="D112" t="s">
+        <v>35</v>
+      </c>
+      <c r="E112" t="s">
+        <v>36</v>
+      </c>
+      <c r="F112" s="1">
+        <v>46085</v>
+      </c>
+      <c r="G112" t="s">
+        <v>375</v>
+      </c>
+      <c r="H112" t="s">
+        <v>376</v>
+      </c>
+      <c r="I112" t="s">
+        <v>377</v>
+      </c>
+      <c r="J112">
+        <v>1</v>
+      </c>
+      <c r="K112">
+        <v>12.29</v>
+      </c>
+      <c r="L112">
+        <v>12.29</v>
+      </c>
+      <c r="M112" t="s">
+        <v>22</v>
+      </c>
+      <c r="N112" t="s">
+        <v>23</v>
+      </c>
+      <c r="O112" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P112" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>24</v>
+      </c>
+      <c r="R112" t="s">
+        <v>41</v>
+      </c>
+      <c r="S112" t="s">
+        <v>25</v>
+      </c>
+      <c r="T112" t="s">
+        <v>42</v>
+      </c>
+      <c r="U112" t="s">
+        <v>43</v>
+      </c>
+      <c r="V112" t="s">
+        <v>44</v>
+      </c>
+      <c r="W112" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>367</v>
+      </c>
+      <c r="B113" t="s">
+        <v>368</v>
+      </c>
+      <c r="C113" t="s">
+        <v>34</v>
+      </c>
+      <c r="D113" t="s">
+        <v>35</v>
+      </c>
+      <c r="E113" t="s">
+        <v>36</v>
+      </c>
+      <c r="F113" s="1">
+        <v>46085</v>
+      </c>
+      <c r="G113" t="s">
+        <v>378</v>
+      </c>
+      <c r="H113" t="s">
+        <v>379</v>
+      </c>
+      <c r="I113" t="s">
+        <v>380</v>
+      </c>
+      <c r="J113">
+        <v>1</v>
+      </c>
+      <c r="K113">
+        <v>13.12</v>
+      </c>
+      <c r="L113">
+        <v>13.12</v>
+      </c>
+      <c r="M113" t="s">
+        <v>22</v>
+      </c>
+      <c r="N113" t="s">
+        <v>23</v>
+      </c>
+      <c r="O113" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P113" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>24</v>
+      </c>
+      <c r="R113" t="s">
+        <v>41</v>
+      </c>
+      <c r="S113" t="s">
+        <v>25</v>
+      </c>
+      <c r="T113" t="s">
+        <v>42</v>
+      </c>
+      <c r="U113" t="s">
+        <v>43</v>
+      </c>
+      <c r="V113" t="s">
+        <v>44</v>
+      </c>
+      <c r="W113" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>367</v>
+      </c>
+      <c r="B114" t="s">
+        <v>368</v>
+      </c>
+      <c r="C114" t="s">
+        <v>34</v>
+      </c>
+      <c r="D114" t="s">
+        <v>35</v>
+      </c>
+      <c r="E114" t="s">
+        <v>36</v>
+      </c>
+      <c r="F114" s="1">
+        <v>46085</v>
+      </c>
+      <c r="G114" t="s">
+        <v>381</v>
+      </c>
+      <c r="H114" t="s">
+        <v>382</v>
+      </c>
+      <c r="I114" t="s">
+        <v>383</v>
+      </c>
+      <c r="J114">
+        <v>1</v>
+      </c>
+      <c r="K114">
+        <v>21.6</v>
+      </c>
+      <c r="L114">
+        <v>21.6</v>
+      </c>
+      <c r="M114" t="s">
+        <v>22</v>
+      </c>
+      <c r="N114" t="s">
+        <v>23</v>
+      </c>
+      <c r="O114" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P114" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>24</v>
+      </c>
+      <c r="R114" t="s">
+        <v>41</v>
+      </c>
+      <c r="S114" t="s">
+        <v>25</v>
+      </c>
+      <c r="T114" t="s">
+        <v>42</v>
+      </c>
+      <c r="U114" t="s">
+        <v>43</v>
+      </c>
+      <c r="V114" t="s">
+        <v>44</v>
+      </c>
+      <c r="W114" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>367</v>
+      </c>
+      <c r="B115" t="s">
+        <v>368</v>
+      </c>
+      <c r="C115" t="s">
+        <v>34</v>
+      </c>
+      <c r="D115" t="s">
+        <v>35</v>
+      </c>
+      <c r="E115" t="s">
+        <v>36</v>
+      </c>
+      <c r="F115" s="1">
+        <v>46085</v>
+      </c>
+      <c r="G115" t="s">
+        <v>72</v>
+      </c>
+      <c r="H115" t="s">
+        <v>73</v>
+      </c>
+      <c r="I115" t="s">
+        <v>74</v>
+      </c>
+      <c r="J115">
+        <v>1</v>
+      </c>
+      <c r="K115">
+        <v>50.32</v>
+      </c>
+      <c r="L115">
+        <v>50.32</v>
+      </c>
+      <c r="M115" t="s">
+        <v>22</v>
+      </c>
+      <c r="N115" t="s">
+        <v>23</v>
+      </c>
+      <c r="O115" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P115" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>24</v>
+      </c>
+      <c r="R115" t="s">
+        <v>41</v>
+      </c>
+      <c r="S115" t="s">
+        <v>25</v>
+      </c>
+      <c r="T115" t="s">
+        <v>42</v>
+      </c>
+      <c r="U115" t="s">
+        <v>43</v>
+      </c>
+      <c r="V115" t="s">
+        <v>44</v>
+      </c>
+      <c r="W115" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>367</v>
+      </c>
+      <c r="B116" t="s">
+        <v>368</v>
+      </c>
+      <c r="C116" t="s">
+        <v>34</v>
+      </c>
+      <c r="D116" t="s">
+        <v>35</v>
+      </c>
+      <c r="E116" t="s">
+        <v>36</v>
+      </c>
+      <c r="F116" s="1">
+        <v>46085</v>
+      </c>
+      <c r="G116" t="s">
+        <v>75</v>
+      </c>
+      <c r="H116" t="s">
+        <v>76</v>
+      </c>
+      <c r="I116" t="s">
+        <v>77</v>
+      </c>
+      <c r="J116">
+        <v>12</v>
+      </c>
+      <c r="K116">
+        <v>10.050000000000001</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116" t="s">
+        <v>22</v>
+      </c>
+      <c r="N116" t="s">
+        <v>23</v>
+      </c>
+      <c r="O116" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P116" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>24</v>
+      </c>
+      <c r="R116" t="s">
+        <v>41</v>
+      </c>
+      <c r="S116" t="s">
+        <v>25</v>
+      </c>
+      <c r="T116" t="s">
+        <v>42</v>
+      </c>
+      <c r="U116" t="s">
+        <v>43</v>
+      </c>
+      <c r="V116" t="s">
+        <v>44</v>
+      </c>
+      <c r="W116" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>384</v>
+      </c>
+      <c r="B117" t="s">
+        <v>385</v>
+      </c>
+      <c r="C117" t="s">
+        <v>34</v>
+      </c>
+      <c r="D117" t="s">
+        <v>35</v>
+      </c>
+      <c r="E117" t="s">
+        <v>36</v>
+      </c>
+      <c r="F117" s="1">
+        <v>46086</v>
+      </c>
+      <c r="G117" t="s">
+        <v>386</v>
+      </c>
+      <c r="H117" t="s">
+        <v>387</v>
+      </c>
+      <c r="I117" t="s">
+        <v>388</v>
+      </c>
+      <c r="J117">
+        <v>48</v>
+      </c>
+      <c r="K117">
+        <v>10.83</v>
+      </c>
+      <c r="L117">
+        <v>519.84</v>
+      </c>
+      <c r="M117" t="s">
+        <v>22</v>
+      </c>
+      <c r="N117" t="s">
+        <v>23</v>
+      </c>
+      <c r="O117" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P117" t="s">
+        <v>389</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>24</v>
+      </c>
+      <c r="R117" t="s">
+        <v>41</v>
+      </c>
+      <c r="S117" t="s">
+        <v>25</v>
+      </c>
+      <c r="T117" t="s">
+        <v>42</v>
+      </c>
+      <c r="U117" t="s">
+        <v>43</v>
+      </c>
+      <c r="V117" t="s">
+        <v>44</v>
+      </c>
+      <c r="W117" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>384</v>
+      </c>
+      <c r="B118" t="s">
+        <v>385</v>
+      </c>
+      <c r="C118" t="s">
+        <v>34</v>
+      </c>
+      <c r="D118" t="s">
+        <v>35</v>
+      </c>
+      <c r="E118" t="s">
+        <v>36</v>
+      </c>
+      <c r="F118" s="1">
+        <v>46086</v>
+      </c>
+      <c r="G118" t="s">
+        <v>26</v>
+      </c>
+      <c r="H118" t="s">
+        <v>27</v>
+      </c>
+      <c r="I118" t="s">
+        <v>28</v>
+      </c>
+      <c r="J118">
+        <v>60</v>
+      </c>
+      <c r="K118">
+        <v>3.14</v>
+      </c>
+      <c r="L118">
+        <v>188.4</v>
+      </c>
+      <c r="M118" t="s">
+        <v>22</v>
+      </c>
+      <c r="N118" t="s">
+        <v>23</v>
+      </c>
+      <c r="O118" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P118" t="s">
+        <v>389</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>24</v>
+      </c>
+      <c r="R118" t="s">
+        <v>41</v>
+      </c>
+      <c r="S118" t="s">
+        <v>25</v>
+      </c>
+      <c r="T118" t="s">
+        <v>42</v>
+      </c>
+      <c r="U118" t="s">
+        <v>43</v>
+      </c>
+      <c r="V118" t="s">
+        <v>44</v>
+      </c>
+      <c r="W118" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="119" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>384</v>
+      </c>
+      <c r="B119" t="s">
+        <v>385</v>
+      </c>
+      <c r="C119" t="s">
+        <v>34</v>
+      </c>
+      <c r="D119" t="s">
+        <v>35</v>
+      </c>
+      <c r="E119" t="s">
+        <v>36</v>
+      </c>
+      <c r="F119" s="1">
+        <v>46086</v>
+      </c>
+      <c r="G119" t="s">
+        <v>242</v>
+      </c>
+      <c r="H119" t="s">
+        <v>243</v>
+      </c>
+      <c r="I119" t="s">
+        <v>244</v>
+      </c>
+      <c r="J119">
+        <v>24</v>
+      </c>
+      <c r="K119">
+        <v>16.420000000000002</v>
+      </c>
+      <c r="L119">
+        <v>394.08</v>
+      </c>
+      <c r="M119" t="s">
+        <v>22</v>
+      </c>
+      <c r="N119" t="s">
+        <v>23</v>
+      </c>
+      <c r="O119" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P119" t="s">
+        <v>389</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>24</v>
+      </c>
+      <c r="R119" t="s">
+        <v>41</v>
+      </c>
+      <c r="S119" t="s">
+        <v>25</v>
+      </c>
+      <c r="T119" t="s">
+        <v>42</v>
+      </c>
+      <c r="U119" t="s">
+        <v>43</v>
+      </c>
+      <c r="V119" t="s">
+        <v>44</v>
+      </c>
+      <c r="W119" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="120" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>384</v>
+      </c>
+      <c r="B120" t="s">
+        <v>385</v>
+      </c>
+      <c r="C120" t="s">
+        <v>34</v>
+      </c>
+      <c r="D120" t="s">
+        <v>35</v>
+      </c>
+      <c r="E120" t="s">
+        <v>36</v>
+      </c>
+      <c r="F120" s="1">
+        <v>46086</v>
+      </c>
+      <c r="G120" t="s">
+        <v>390</v>
+      </c>
+      <c r="H120" t="s">
+        <v>391</v>
+      </c>
+      <c r="I120" t="s">
+        <v>392</v>
+      </c>
+      <c r="J120">
+        <v>2</v>
+      </c>
+      <c r="K120">
+        <v>16.05</v>
+      </c>
+      <c r="L120">
+        <v>32.1</v>
+      </c>
+      <c r="M120" t="s">
+        <v>22</v>
+      </c>
+      <c r="N120" t="s">
+        <v>23</v>
+      </c>
+      <c r="O120" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P120" t="s">
+        <v>389</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>24</v>
+      </c>
+      <c r="R120" t="s">
+        <v>41</v>
+      </c>
+      <c r="S120" t="s">
+        <v>25</v>
+      </c>
+      <c r="T120" t="s">
+        <v>42</v>
+      </c>
+      <c r="U120" t="s">
+        <v>43</v>
+      </c>
+      <c r="V120" t="s">
+        <v>44</v>
+      </c>
+      <c r="W120" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="121" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>393</v>
+      </c>
+      <c r="B121" t="s">
+        <v>394</v>
+      </c>
+      <c r="C121" t="s">
+        <v>34</v>
+      </c>
+      <c r="D121" t="s">
+        <v>35</v>
+      </c>
+      <c r="E121" t="s">
+        <v>36</v>
+      </c>
+      <c r="F121" s="1">
+        <v>46086</v>
+      </c>
+      <c r="G121" t="s">
+        <v>395</v>
+      </c>
+      <c r="H121" t="s">
+        <v>396</v>
+      </c>
+      <c r="I121" t="s">
+        <v>397</v>
+      </c>
+      <c r="J121">
+        <v>2</v>
+      </c>
+      <c r="K121">
+        <v>31.14</v>
+      </c>
+      <c r="L121">
+        <v>62.28</v>
+      </c>
+      <c r="M121" t="s">
+        <v>22</v>
+      </c>
+      <c r="N121" t="s">
+        <v>23</v>
+      </c>
+      <c r="O121" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P121" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>24</v>
+      </c>
+      <c r="R121" t="s">
+        <v>41</v>
+      </c>
+      <c r="S121" t="s">
+        <v>25</v>
+      </c>
+      <c r="T121" t="s">
+        <v>42</v>
+      </c>
+      <c r="U121" t="s">
+        <v>43</v>
+      </c>
+      <c r="V121" t="s">
+        <v>44</v>
+      </c>
+      <c r="W121" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="122" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>393</v>
+      </c>
+      <c r="B122" t="s">
+        <v>394</v>
+      </c>
+      <c r="C122" t="s">
+        <v>34</v>
+      </c>
+      <c r="D122" t="s">
+        <v>35</v>
+      </c>
+      <c r="E122" t="s">
+        <v>36</v>
+      </c>
+      <c r="F122" s="1">
+        <v>46086</v>
+      </c>
+      <c r="G122" t="s">
+        <v>146</v>
+      </c>
+      <c r="H122" t="s">
+        <v>147</v>
+      </c>
+      <c r="I122" t="s">
+        <v>148</v>
+      </c>
+      <c r="J122">
+        <v>1</v>
+      </c>
+      <c r="K122">
+        <v>29.57</v>
+      </c>
+      <c r="L122">
+        <v>29.57</v>
+      </c>
+      <c r="M122" t="s">
+        <v>22</v>
+      </c>
+      <c r="N122" t="s">
+        <v>23</v>
+      </c>
+      <c r="O122" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P122" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>24</v>
+      </c>
+      <c r="R122" t="s">
+        <v>41</v>
+      </c>
+      <c r="S122" t="s">
+        <v>25</v>
+      </c>
+      <c r="T122" t="s">
+        <v>42</v>
+      </c>
+      <c r="U122" t="s">
+        <v>43</v>
+      </c>
+      <c r="V122" t="s">
+        <v>44</v>
+      </c>
+      <c r="W122" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="123" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>393</v>
+      </c>
+      <c r="B123" t="s">
+        <v>394</v>
+      </c>
+      <c r="C123" t="s">
+        <v>34</v>
+      </c>
+      <c r="D123" t="s">
+        <v>35</v>
+      </c>
+      <c r="E123" t="s">
+        <v>36</v>
+      </c>
+      <c r="F123" s="1">
+        <v>46086</v>
+      </c>
+      <c r="G123" t="s">
+        <v>150</v>
+      </c>
+      <c r="H123" t="s">
+        <v>151</v>
+      </c>
+      <c r="I123" t="s">
+        <v>152</v>
+      </c>
+      <c r="J123">
+        <v>5</v>
+      </c>
+      <c r="K123">
+        <v>13.42</v>
+      </c>
+      <c r="L123">
+        <v>67.099999999999994</v>
+      </c>
+      <c r="M123" t="s">
+        <v>22</v>
+      </c>
+      <c r="N123" t="s">
+        <v>23</v>
+      </c>
+      <c r="O123" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P123" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>24</v>
+      </c>
+      <c r="R123" t="s">
+        <v>41</v>
+      </c>
+      <c r="S123" t="s">
+        <v>25</v>
+      </c>
+      <c r="T123" t="s">
+        <v>42</v>
+      </c>
+      <c r="U123" t="s">
+        <v>43</v>
+      </c>
+      <c r="V123" t="s">
+        <v>44</v>
+      </c>
+      <c r="W123" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="124" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>393</v>
+      </c>
+      <c r="B124" t="s">
+        <v>394</v>
+      </c>
+      <c r="C124" t="s">
+        <v>34</v>
+      </c>
+      <c r="D124" t="s">
+        <v>35</v>
+      </c>
+      <c r="E124" t="s">
+        <v>36</v>
+      </c>
+      <c r="F124" s="1">
+        <v>46086</v>
+      </c>
+      <c r="G124" t="s">
+        <v>399</v>
+      </c>
+      <c r="H124" t="s">
+        <v>400</v>
+      </c>
+      <c r="I124" t="s">
+        <v>401</v>
+      </c>
+      <c r="J124">
+        <v>2</v>
+      </c>
+      <c r="K124">
+        <v>45.13</v>
+      </c>
+      <c r="L124">
+        <v>90.26</v>
+      </c>
+      <c r="M124" t="s">
+        <v>22</v>
+      </c>
+      <c r="N124" t="s">
+        <v>23</v>
+      </c>
+      <c r="O124" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P124" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>24</v>
+      </c>
+      <c r="R124" t="s">
+        <v>41</v>
+      </c>
+      <c r="S124" t="s">
+        <v>25</v>
+      </c>
+      <c r="T124" t="s">
+        <v>42</v>
+      </c>
+      <c r="U124" t="s">
+        <v>43</v>
+      </c>
+      <c r="V124" t="s">
+        <v>44</v>
+      </c>
+      <c r="W124" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="125" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>393</v>
+      </c>
+      <c r="B125" t="s">
+        <v>394</v>
+      </c>
+      <c r="C125" t="s">
+        <v>34</v>
+      </c>
+      <c r="D125" t="s">
+        <v>35</v>
+      </c>
+      <c r="E125" t="s">
+        <v>36</v>
+      </c>
+      <c r="F125" s="1">
+        <v>46086</v>
+      </c>
+      <c r="G125" t="s">
+        <v>93</v>
+      </c>
+      <c r="H125" t="s">
+        <v>94</v>
+      </c>
+      <c r="I125" t="s">
+        <v>95</v>
+      </c>
+      <c r="J125">
+        <v>2</v>
+      </c>
+      <c r="K125">
+        <v>13.33</v>
+      </c>
+      <c r="L125">
+        <v>26.66</v>
+      </c>
+      <c r="M125" t="s">
+        <v>22</v>
+      </c>
+      <c r="N125" t="s">
+        <v>23</v>
+      </c>
+      <c r="O125" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P125" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>24</v>
+      </c>
+      <c r="R125" t="s">
+        <v>41</v>
+      </c>
+      <c r="S125" t="s">
+        <v>25</v>
+      </c>
+      <c r="T125" t="s">
+        <v>42</v>
+      </c>
+      <c r="U125" t="s">
+        <v>43</v>
+      </c>
+      <c r="V125" t="s">
+        <v>44</v>
+      </c>
+      <c r="W125" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="126" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>393</v>
+      </c>
+      <c r="B126" t="s">
+        <v>394</v>
+      </c>
+      <c r="C126" t="s">
+        <v>34</v>
+      </c>
+      <c r="D126" t="s">
+        <v>35</v>
+      </c>
+      <c r="E126" t="s">
+        <v>36</v>
+      </c>
+      <c r="F126" s="1">
+        <v>46086</v>
+      </c>
+      <c r="G126" t="s">
+        <v>402</v>
+      </c>
+      <c r="H126" t="s">
+        <v>403</v>
+      </c>
+      <c r="I126" t="s">
+        <v>404</v>
+      </c>
+      <c r="J126">
+        <v>1</v>
+      </c>
+      <c r="K126">
+        <v>14.9</v>
+      </c>
+      <c r="L126">
+        <v>14.9</v>
+      </c>
+      <c r="M126" t="s">
+        <v>22</v>
+      </c>
+      <c r="N126" t="s">
+        <v>23</v>
+      </c>
+      <c r="O126" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P126" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>24</v>
+      </c>
+      <c r="R126" t="s">
+        <v>41</v>
+      </c>
+      <c r="S126" t="s">
+        <v>25</v>
+      </c>
+      <c r="T126" t="s">
+        <v>42</v>
+      </c>
+      <c r="U126" t="s">
+        <v>43</v>
+      </c>
+      <c r="V126" t="s">
+        <v>44</v>
+      </c>
+      <c r="W126" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="127" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>393</v>
+      </c>
+      <c r="B127" t="s">
+        <v>394</v>
+      </c>
+      <c r="C127" t="s">
+        <v>34</v>
+      </c>
+      <c r="D127" t="s">
+        <v>35</v>
+      </c>
+      <c r="E127" t="s">
+        <v>36</v>
+      </c>
+      <c r="F127" s="1">
+        <v>46086</v>
+      </c>
+      <c r="G127" t="s">
+        <v>405</v>
+      </c>
+      <c r="H127" t="s">
+        <v>406</v>
+      </c>
+      <c r="I127" t="s">
+        <v>407</v>
+      </c>
+      <c r="J127">
+        <v>2</v>
+      </c>
+      <c r="K127">
+        <v>28.29</v>
+      </c>
+      <c r="L127">
+        <v>56.58</v>
+      </c>
+      <c r="M127" t="s">
+        <v>22</v>
+      </c>
+      <c r="N127" t="s">
+        <v>23</v>
+      </c>
+      <c r="O127" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P127" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>24</v>
+      </c>
+      <c r="R127" t="s">
+        <v>41</v>
+      </c>
+      <c r="S127" t="s">
+        <v>25</v>
+      </c>
+      <c r="T127" t="s">
+        <v>42</v>
+      </c>
+      <c r="U127" t="s">
+        <v>43</v>
+      </c>
+      <c r="V127" t="s">
+        <v>44</v>
+      </c>
+      <c r="W127" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="128" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>408</v>
+      </c>
+      <c r="B128" t="s">
+        <v>409</v>
+      </c>
+      <c r="C128" t="s">
+        <v>34</v>
+      </c>
+      <c r="D128" t="s">
+        <v>35</v>
+      </c>
+      <c r="E128" t="s">
+        <v>36</v>
+      </c>
+      <c r="F128" s="1">
+        <v>46087</v>
+      </c>
+      <c r="G128" t="s">
+        <v>410</v>
+      </c>
+      <c r="H128" t="s">
+        <v>411</v>
+      </c>
+      <c r="I128" t="s">
+        <v>412</v>
+      </c>
+      <c r="J128">
+        <v>2</v>
+      </c>
+      <c r="K128">
+        <v>27.49</v>
+      </c>
+      <c r="L128">
+        <v>54.98</v>
+      </c>
+      <c r="M128" t="s">
+        <v>22</v>
+      </c>
+      <c r="N128" t="s">
+        <v>23</v>
+      </c>
+      <c r="O128" s="1">
+        <v>46087</v>
+      </c>
+      <c r="P128" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>24</v>
+      </c>
+      <c r="R128" t="s">
+        <v>41</v>
+      </c>
+      <c r="S128" t="s">
+        <v>25</v>
+      </c>
+      <c r="T128" t="s">
+        <v>42</v>
+      </c>
+      <c r="U128" t="s">
+        <v>43</v>
+      </c>
+      <c r="V128" t="s">
+        <v>44</v>
+      </c>
+      <c r="W128" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="129" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>408</v>
+      </c>
+      <c r="B129" t="s">
+        <v>409</v>
+      </c>
+      <c r="C129" t="s">
+        <v>34</v>
+      </c>
+      <c r="D129" t="s">
+        <v>35</v>
+      </c>
+      <c r="E129" t="s">
+        <v>36</v>
+      </c>
+      <c r="F129" s="1">
+        <v>46087</v>
+      </c>
+      <c r="G129" t="s">
+        <v>105</v>
+      </c>
+      <c r="H129" t="s">
+        <v>106</v>
+      </c>
+      <c r="I129" t="s">
+        <v>107</v>
+      </c>
+      <c r="J129">
+        <v>1</v>
+      </c>
+      <c r="K129">
+        <v>13.87</v>
+      </c>
+      <c r="L129">
+        <v>13.87</v>
+      </c>
+      <c r="M129" t="s">
+        <v>22</v>
+      </c>
+      <c r="N129" t="s">
+        <v>23</v>
+      </c>
+      <c r="O129" s="1">
+        <v>46087</v>
+      </c>
+      <c r="P129" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>24</v>
+      </c>
+      <c r="R129" t="s">
+        <v>41</v>
+      </c>
+      <c r="S129" t="s">
+        <v>25</v>
+      </c>
+      <c r="T129" t="s">
+        <v>42</v>
+      </c>
+      <c r="U129" t="s">
+        <v>43</v>
+      </c>
+      <c r="V129" t="s">
+        <v>44</v>
+      </c>
+      <c r="W129" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="130" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>408</v>
+      </c>
+      <c r="B130" t="s">
+        <v>409</v>
+      </c>
+      <c r="C130" t="s">
+        <v>34</v>
+      </c>
+      <c r="D130" t="s">
+        <v>35</v>
+      </c>
+      <c r="E130" t="s">
+        <v>36</v>
+      </c>
+      <c r="F130" s="1">
+        <v>46087</v>
+      </c>
+      <c r="G130" t="s">
+        <v>239</v>
+      </c>
+      <c r="H130" t="s">
+        <v>240</v>
+      </c>
+      <c r="I130" t="s">
+        <v>241</v>
+      </c>
+      <c r="J130">
+        <v>2</v>
+      </c>
+      <c r="K130">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="L130">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="M130" t="s">
+        <v>22</v>
+      </c>
+      <c r="N130" t="s">
+        <v>23</v>
+      </c>
+      <c r="O130" s="1">
+        <v>46087</v>
+      </c>
+      <c r="P130" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>24</v>
+      </c>
+      <c r="R130" t="s">
+        <v>41</v>
+      </c>
+      <c r="S130" t="s">
+        <v>25</v>
+      </c>
+      <c r="T130" t="s">
+        <v>42</v>
+      </c>
+      <c r="U130" t="s">
+        <v>43</v>
+      </c>
+      <c r="V130" t="s">
+        <v>44</v>
+      </c>
+      <c r="W130" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="131" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>408</v>
+      </c>
+      <c r="B131" t="s">
+        <v>409</v>
+      </c>
+      <c r="C131" t="s">
+        <v>34</v>
+      </c>
+      <c r="D131" t="s">
+        <v>35</v>
+      </c>
+      <c r="E131" t="s">
+        <v>36</v>
+      </c>
+      <c r="F131" s="1">
+        <v>46087</v>
+      </c>
+      <c r="G131" t="s">
+        <v>414</v>
+      </c>
+      <c r="H131" t="s">
+        <v>415</v>
+      </c>
+      <c r="I131" t="s">
+        <v>416</v>
+      </c>
+      <c r="J131">
+        <v>1</v>
+      </c>
+      <c r="K131">
+        <v>15.87</v>
+      </c>
+      <c r="L131">
+        <v>15.87</v>
+      </c>
+      <c r="M131" t="s">
+        <v>22</v>
+      </c>
+      <c r="N131" t="s">
+        <v>23</v>
+      </c>
+      <c r="O131" s="1">
+        <v>46087</v>
+      </c>
+      <c r="P131" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>24</v>
+      </c>
+      <c r="R131" t="s">
+        <v>41</v>
+      </c>
+      <c r="S131" t="s">
+        <v>25</v>
+      </c>
+      <c r="T131" t="s">
+        <v>42</v>
+      </c>
+      <c r="U131" t="s">
+        <v>43</v>
+      </c>
+      <c r="V131" t="s">
+        <v>44</v>
+      </c>
+      <c r="W131" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="132" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>408</v>
+      </c>
+      <c r="B132" t="s">
+        <v>409</v>
+      </c>
+      <c r="C132" t="s">
+        <v>34</v>
+      </c>
+      <c r="D132" t="s">
+        <v>35</v>
+      </c>
+      <c r="E132" t="s">
+        <v>36</v>
+      </c>
+      <c r="F132" s="1">
+        <v>46087</v>
+      </c>
+      <c r="G132" t="s">
+        <v>417</v>
+      </c>
+      <c r="H132" t="s">
+        <v>418</v>
+      </c>
+      <c r="I132" t="s">
+        <v>419</v>
+      </c>
+      <c r="J132">
+        <v>2</v>
+      </c>
+      <c r="K132">
+        <v>23.51</v>
+      </c>
+      <c r="L132">
+        <v>47.02</v>
+      </c>
+      <c r="M132" t="s">
+        <v>22</v>
+      </c>
+      <c r="N132" t="s">
+        <v>23</v>
+      </c>
+      <c r="O132" s="1">
+        <v>46087</v>
+      </c>
+      <c r="P132" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>24</v>
+      </c>
+      <c r="R132" t="s">
+        <v>41</v>
+      </c>
+      <c r="S132" t="s">
+        <v>25</v>
+      </c>
+      <c r="T132" t="s">
+        <v>42</v>
+      </c>
+      <c r="U132" t="s">
+        <v>43</v>
+      </c>
+      <c r="V132" t="s">
+        <v>44</v>
+      </c>
+      <c r="W132" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="133" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>408</v>
+      </c>
+      <c r="B133" t="s">
+        <v>409</v>
+      </c>
+      <c r="C133" t="s">
+        <v>34</v>
+      </c>
+      <c r="D133" t="s">
+        <v>35</v>
+      </c>
+      <c r="E133" t="s">
+        <v>36</v>
+      </c>
+      <c r="F133" s="1">
+        <v>46087</v>
+      </c>
+      <c r="G133" t="s">
+        <v>141</v>
+      </c>
+      <c r="H133" t="s">
+        <v>142</v>
+      </c>
+      <c r="I133" t="s">
+        <v>143</v>
+      </c>
+      <c r="J133">
+        <v>2</v>
+      </c>
+      <c r="K133">
+        <v>18.68</v>
+      </c>
+      <c r="L133">
+        <v>37.36</v>
+      </c>
+      <c r="M133" t="s">
+        <v>22</v>
+      </c>
+      <c r="N133" t="s">
+        <v>23</v>
+      </c>
+      <c r="O133" s="1">
+        <v>46087</v>
+      </c>
+      <c r="P133" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>24</v>
+      </c>
+      <c r="R133" t="s">
+        <v>41</v>
+      </c>
+      <c r="S133" t="s">
+        <v>25</v>
+      </c>
+      <c r="T133" t="s">
+        <v>42</v>
+      </c>
+      <c r="U133" t="s">
+        <v>43</v>
+      </c>
+      <c r="V133" t="s">
+        <v>44</v>
+      </c>
+      <c r="W133" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="134" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>420</v>
+      </c>
+      <c r="B134" t="s">
+        <v>421</v>
+      </c>
+      <c r="C134" t="s">
+        <v>34</v>
+      </c>
+      <c r="D134" t="s">
+        <v>35</v>
+      </c>
+      <c r="E134" t="s">
+        <v>36</v>
+      </c>
+      <c r="F134" s="1">
+        <v>46090</v>
+      </c>
+      <c r="G134" t="s">
+        <v>29</v>
+      </c>
+      <c r="H134" t="s">
+        <v>30</v>
+      </c>
+      <c r="I134" t="s">
+        <v>31</v>
+      </c>
+      <c r="J134">
+        <v>1</v>
+      </c>
+      <c r="K134">
+        <v>20.18</v>
+      </c>
+      <c r="L134">
+        <v>20.18</v>
+      </c>
+      <c r="M134" t="s">
+        <v>22</v>
+      </c>
+      <c r="N134" t="s">
+        <v>23</v>
+      </c>
+      <c r="O134" s="1">
+        <v>46087</v>
+      </c>
+      <c r="P134" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>24</v>
+      </c>
+      <c r="R134" t="s">
+        <v>41</v>
+      </c>
+      <c r="S134" t="s">
+        <v>25</v>
+      </c>
+      <c r="T134" t="s">
+        <v>42</v>
+      </c>
+      <c r="U134" t="s">
+        <v>43</v>
+      </c>
+      <c r="V134" t="s">
+        <v>44</v>
+      </c>
+      <c r="W134" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="135" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>420</v>
+      </c>
+      <c r="B135" t="s">
+        <v>421</v>
+      </c>
+      <c r="C135" t="s">
+        <v>34</v>
+      </c>
+      <c r="D135" t="s">
+        <v>35</v>
+      </c>
+      <c r="E135" t="s">
+        <v>36</v>
+      </c>
+      <c r="F135" s="1">
+        <v>46090</v>
+      </c>
+      <c r="G135" t="s">
+        <v>410</v>
+      </c>
+      <c r="H135" t="s">
+        <v>411</v>
+      </c>
+      <c r="I135" t="s">
+        <v>412</v>
+      </c>
+      <c r="J135">
+        <v>1</v>
+      </c>
+      <c r="K135">
+        <v>27.49</v>
+      </c>
+      <c r="L135">
+        <v>27.49</v>
+      </c>
+      <c r="M135" t="s">
+        <v>22</v>
+      </c>
+      <c r="N135" t="s">
+        <v>23</v>
+      </c>
+      <c r="O135" s="1">
+        <v>46087</v>
+      </c>
+      <c r="P135" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>24</v>
+      </c>
+      <c r="R135" t="s">
+        <v>41</v>
+      </c>
+      <c r="S135" t="s">
+        <v>25</v>
+      </c>
+      <c r="T135" t="s">
+        <v>42</v>
+      </c>
+      <c r="U135" t="s">
+        <v>43</v>
+      </c>
+      <c r="V135" t="s">
+        <v>44</v>
+      </c>
+      <c r="W135" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="136" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>420</v>
+      </c>
+      <c r="B136" t="s">
+        <v>421</v>
+      </c>
+      <c r="C136" t="s">
+        <v>34</v>
+      </c>
+      <c r="D136" t="s">
+        <v>35</v>
+      </c>
+      <c r="E136" t="s">
+        <v>36</v>
+      </c>
+      <c r="F136" s="1">
+        <v>46090</v>
+      </c>
+      <c r="G136" t="s">
+        <v>150</v>
+      </c>
+      <c r="H136" t="s">
+        <v>151</v>
+      </c>
+      <c r="I136" t="s">
+        <v>152</v>
+      </c>
+      <c r="J136">
+        <v>2</v>
+      </c>
+      <c r="K136">
+        <v>13.42</v>
+      </c>
+      <c r="L136">
+        <v>26.84</v>
+      </c>
+      <c r="M136" t="s">
+        <v>22</v>
+      </c>
+      <c r="N136" t="s">
+        <v>23</v>
+      </c>
+      <c r="O136" s="1">
+        <v>46087</v>
+      </c>
+      <c r="P136" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>24</v>
+      </c>
+      <c r="R136" t="s">
+        <v>41</v>
+      </c>
+      <c r="S136" t="s">
+        <v>25</v>
+      </c>
+      <c r="T136" t="s">
+        <v>42</v>
+      </c>
+      <c r="U136" t="s">
+        <v>43</v>
+      </c>
+      <c r="V136" t="s">
+        <v>44</v>
+      </c>
+      <c r="W136" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="137" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>420</v>
+      </c>
+      <c r="B137" t="s">
+        <v>421</v>
+      </c>
+      <c r="C137" t="s">
+        <v>34</v>
+      </c>
+      <c r="D137" t="s">
+        <v>35</v>
+      </c>
+      <c r="E137" t="s">
+        <v>36</v>
+      </c>
+      <c r="F137" s="1">
+        <v>46090</v>
+      </c>
+      <c r="G137" t="s">
+        <v>422</v>
+      </c>
+      <c r="H137" t="s">
+        <v>423</v>
+      </c>
+      <c r="I137" t="s">
+        <v>424</v>
+      </c>
+      <c r="J137">
+        <v>1</v>
+      </c>
+      <c r="K137">
+        <v>14.79</v>
+      </c>
+      <c r="L137">
+        <v>14.79</v>
+      </c>
+      <c r="M137" t="s">
+        <v>22</v>
+      </c>
+      <c r="N137" t="s">
+        <v>23</v>
+      </c>
+      <c r="O137" s="1">
+        <v>46087</v>
+      </c>
+      <c r="P137" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>24</v>
+      </c>
+      <c r="R137" t="s">
+        <v>41</v>
+      </c>
+      <c r="S137" t="s">
+        <v>25</v>
+      </c>
+      <c r="T137" t="s">
+        <v>42</v>
+      </c>
+      <c r="U137" t="s">
+        <v>43</v>
+      </c>
+      <c r="V137" t="s">
+        <v>44</v>
+      </c>
+      <c r="W137" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="138" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>420</v>
+      </c>
+      <c r="B138" t="s">
+        <v>421</v>
+      </c>
+      <c r="C138" t="s">
+        <v>34</v>
+      </c>
+      <c r="D138" t="s">
+        <v>35</v>
+      </c>
+      <c r="E138" t="s">
+        <v>36</v>
+      </c>
+      <c r="F138" s="1">
+        <v>46090</v>
+      </c>
+      <c r="G138" t="s">
+        <v>381</v>
+      </c>
+      <c r="H138" t="s">
+        <v>382</v>
+      </c>
+      <c r="I138" t="s">
+        <v>383</v>
+      </c>
+      <c r="J138">
+        <v>1</v>
+      </c>
+      <c r="K138">
+        <v>21.6</v>
+      </c>
+      <c r="L138">
+        <v>21.6</v>
+      </c>
+      <c r="M138" t="s">
+        <v>22</v>
+      </c>
+      <c r="N138" t="s">
+        <v>23</v>
+      </c>
+      <c r="O138" s="1">
+        <v>46087</v>
+      </c>
+      <c r="P138" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>24</v>
+      </c>
+      <c r="R138" t="s">
+        <v>41</v>
+      </c>
+      <c r="S138" t="s">
+        <v>25</v>
+      </c>
+      <c r="T138" t="s">
+        <v>42</v>
+      </c>
+      <c r="U138" t="s">
+        <v>43</v>
+      </c>
+      <c r="V138" t="s">
+        <v>44</v>
+      </c>
+      <c r="W138" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="139" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>420</v>
+      </c>
+      <c r="B139" t="s">
+        <v>421</v>
+      </c>
+      <c r="C139" t="s">
+        <v>34</v>
+      </c>
+      <c r="D139" t="s">
+        <v>35</v>
+      </c>
+      <c r="E139" t="s">
+        <v>36</v>
+      </c>
+      <c r="F139" s="1">
+        <v>46090</v>
+      </c>
+      <c r="G139" t="s">
+        <v>390</v>
+      </c>
+      <c r="H139" t="s">
+        <v>391</v>
+      </c>
+      <c r="I139" t="s">
+        <v>392</v>
+      </c>
+      <c r="J139">
+        <v>1</v>
+      </c>
+      <c r="K139">
+        <v>16.05</v>
+      </c>
+      <c r="L139">
+        <v>16.05</v>
+      </c>
+      <c r="M139" t="s">
+        <v>22</v>
+      </c>
+      <c r="N139" t="s">
+        <v>23</v>
+      </c>
+      <c r="O139" s="1">
+        <v>46087</v>
+      </c>
+      <c r="P139" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>24</v>
+      </c>
+      <c r="R139" t="s">
+        <v>41</v>
+      </c>
+      <c r="S139" t="s">
+        <v>25</v>
+      </c>
+      <c r="T139" t="s">
+        <v>42</v>
+      </c>
+      <c r="U139" t="s">
+        <v>43</v>
+      </c>
+      <c r="V139" t="s">
+        <v>44</v>
+      </c>
+      <c r="W139" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="140" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>420</v>
+      </c>
+      <c r="B140" t="s">
+        <v>421</v>
+      </c>
+      <c r="C140" t="s">
+        <v>34</v>
+      </c>
+      <c r="D140" t="s">
+        <v>35</v>
+      </c>
+      <c r="E140" t="s">
+        <v>36</v>
+      </c>
+      <c r="F140" s="1">
+        <v>46090</v>
+      </c>
+      <c r="G140" t="s">
+        <v>425</v>
+      </c>
+      <c r="H140" t="s">
+        <v>426</v>
+      </c>
+      <c r="I140" t="s">
+        <v>427</v>
+      </c>
+      <c r="J140">
+        <v>1</v>
+      </c>
+      <c r="K140">
+        <v>53.4</v>
+      </c>
+      <c r="L140">
+        <v>53.4</v>
+      </c>
+      <c r="M140" t="s">
+        <v>22</v>
+      </c>
+      <c r="N140" t="s">
+        <v>23</v>
+      </c>
+      <c r="O140" s="1">
+        <v>46087</v>
+      </c>
+      <c r="P140" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>24</v>
+      </c>
+      <c r="R140" t="s">
+        <v>41</v>
+      </c>
+      <c r="S140" t="s">
+        <v>25</v>
+      </c>
+      <c r="T140" t="s">
+        <v>42</v>
+      </c>
+      <c r="U140" t="s">
+        <v>43</v>
+      </c>
+      <c r="V140" t="s">
+        <v>44</v>
+      </c>
+      <c r="W140" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="141" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>420</v>
+      </c>
+      <c r="B141" t="s">
+        <v>421</v>
+      </c>
+      <c r="C141" t="s">
+        <v>34</v>
+      </c>
+      <c r="D141" t="s">
+        <v>35</v>
+      </c>
+      <c r="E141" t="s">
+        <v>36</v>
+      </c>
+      <c r="F141" s="1">
+        <v>46090</v>
+      </c>
+      <c r="G141" t="s">
+        <v>428</v>
+      </c>
+      <c r="H141" t="s">
+        <v>429</v>
+      </c>
+      <c r="I141" t="s">
+        <v>430</v>
+      </c>
+      <c r="J141">
+        <v>1</v>
+      </c>
+      <c r="K141">
+        <v>4.68</v>
+      </c>
+      <c r="L141">
+        <v>4.68</v>
+      </c>
+      <c r="M141" t="s">
+        <v>22</v>
+      </c>
+      <c r="N141" t="s">
+        <v>23</v>
+      </c>
+      <c r="O141" s="1">
+        <v>46087</v>
+      </c>
+      <c r="P141" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>24</v>
+      </c>
+      <c r="R141" t="s">
+        <v>41</v>
+      </c>
+      <c r="S141" t="s">
+        <v>25</v>
+      </c>
+      <c r="T141" t="s">
+        <v>42</v>
+      </c>
+      <c r="U141" t="s">
+        <v>43</v>
+      </c>
+      <c r="V141" t="s">
+        <v>44</v>
+      </c>
+      <c r="W141" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="142" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>431</v>
+      </c>
+      <c r="B142" t="s">
+        <v>432</v>
+      </c>
+      <c r="C142" t="s">
+        <v>34</v>
+      </c>
+      <c r="D142" t="s">
+        <v>35</v>
+      </c>
+      <c r="E142" t="s">
+        <v>36</v>
+      </c>
+      <c r="F142" s="1">
+        <v>46087</v>
+      </c>
+      <c r="G142" t="s">
+        <v>433</v>
+      </c>
+      <c r="H142" t="s">
+        <v>434</v>
+      </c>
+      <c r="I142" t="s">
+        <v>435</v>
+      </c>
+      <c r="J142">
+        <v>1</v>
+      </c>
+      <c r="K142">
+        <v>13.37</v>
+      </c>
+      <c r="L142">
+        <v>13.37</v>
+      </c>
+      <c r="M142" t="s">
+        <v>22</v>
+      </c>
+      <c r="N142" t="s">
+        <v>23</v>
+      </c>
+      <c r="O142" s="1">
+        <v>46087</v>
+      </c>
+      <c r="P142" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>24</v>
+      </c>
+      <c r="R142" t="s">
+        <v>41</v>
+      </c>
+      <c r="S142" t="s">
+        <v>25</v>
+      </c>
+      <c r="T142" t="s">
+        <v>42</v>
+      </c>
+      <c r="U142" t="s">
+        <v>43</v>
+      </c>
+      <c r="V142" t="s">
+        <v>44</v>
+      </c>
+      <c r="W142" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="143" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>436</v>
+      </c>
+      <c r="B143" t="s">
+        <v>437</v>
+      </c>
+      <c r="C143" t="s">
+        <v>34</v>
+      </c>
+      <c r="D143" t="s">
+        <v>35</v>
+      </c>
+      <c r="E143" t="s">
+        <v>36</v>
+      </c>
+      <c r="F143" s="1">
+        <v>46091</v>
+      </c>
+      <c r="G143" t="s">
+        <v>438</v>
+      </c>
+      <c r="H143" t="s">
+        <v>439</v>
+      </c>
+      <c r="I143" t="s">
+        <v>440</v>
+      </c>
+      <c r="J143">
+        <v>1</v>
+      </c>
+      <c r="K143">
+        <v>7.19</v>
+      </c>
+      <c r="L143">
+        <v>7.19</v>
+      </c>
+      <c r="M143" t="s">
+        <v>22</v>
+      </c>
+      <c r="N143" t="s">
+        <v>23</v>
+      </c>
+      <c r="O143" s="1">
+        <v>46090</v>
+      </c>
+      <c r="P143" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>24</v>
+      </c>
+      <c r="R143" t="s">
+        <v>41</v>
+      </c>
+      <c r="S143" t="s">
+        <v>25</v>
+      </c>
+      <c r="T143" t="s">
+        <v>42</v>
+      </c>
+      <c r="U143" t="s">
+        <v>43</v>
+      </c>
+      <c r="V143" t="s">
+        <v>44</v>
+      </c>
+      <c r="W143" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="144" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>436</v>
+      </c>
+      <c r="B144" t="s">
+        <v>437</v>
+      </c>
+      <c r="C144" t="s">
+        <v>34</v>
+      </c>
+      <c r="D144" t="s">
+        <v>35</v>
+      </c>
+      <c r="E144" t="s">
+        <v>36</v>
+      </c>
+      <c r="F144" s="1">
+        <v>46091</v>
+      </c>
+      <c r="G144" t="s">
+        <v>428</v>
+      </c>
+      <c r="H144" t="s">
+        <v>429</v>
+      </c>
+      <c r="I144" t="s">
+        <v>430</v>
+      </c>
+      <c r="J144">
+        <v>6</v>
+      </c>
+      <c r="K144">
+        <v>4.68</v>
+      </c>
+      <c r="L144">
+        <v>28.08</v>
+      </c>
+      <c r="M144" t="s">
+        <v>22</v>
+      </c>
+      <c r="N144" t="s">
+        <v>23</v>
+      </c>
+      <c r="O144" s="1">
+        <v>46090</v>
+      </c>
+      <c r="P144" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>24</v>
+      </c>
+      <c r="R144" t="s">
+        <v>41</v>
+      </c>
+      <c r="S144" t="s">
+        <v>25</v>
+      </c>
+      <c r="T144" t="s">
+        <v>42</v>
+      </c>
+      <c r="U144" t="s">
+        <v>43</v>
+      </c>
+      <c r="V144" t="s">
+        <v>44</v>
+      </c>
+      <c r="W144" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="145" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>441</v>
+      </c>
+      <c r="B145" t="s">
+        <v>442</v>
+      </c>
+      <c r="C145" t="s">
+        <v>34</v>
+      </c>
+      <c r="D145" t="s">
+        <v>35</v>
+      </c>
+      <c r="E145" t="s">
+        <v>36</v>
+      </c>
+      <c r="F145" s="1">
+        <v>46092</v>
+      </c>
+      <c r="G145" t="s">
+        <v>221</v>
+      </c>
+      <c r="H145" t="s">
+        <v>222</v>
+      </c>
+      <c r="I145" t="s">
+        <v>223</v>
+      </c>
+      <c r="J145">
+        <v>6</v>
+      </c>
+      <c r="K145">
+        <v>15.86</v>
+      </c>
+      <c r="L145">
+        <v>95.16</v>
+      </c>
+      <c r="M145" t="s">
+        <v>22</v>
+      </c>
+      <c r="N145" t="s">
+        <v>23</v>
+      </c>
+      <c r="O145" s="1">
+        <v>46092</v>
+      </c>
+      <c r="P145" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>24</v>
+      </c>
+      <c r="R145" t="s">
+        <v>41</v>
+      </c>
+      <c r="S145" t="s">
+        <v>25</v>
+      </c>
+      <c r="T145" t="s">
+        <v>42</v>
+      </c>
+      <c r="U145" t="s">
+        <v>43</v>
+      </c>
+      <c r="V145" t="s">
+        <v>44</v>
+      </c>
+      <c r="W145" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="146" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>444</v>
+      </c>
+      <c r="B146" t="s">
+        <v>445</v>
+      </c>
+      <c r="C146" t="s">
+        <v>34</v>
+      </c>
+      <c r="D146" t="s">
+        <v>35</v>
+      </c>
+      <c r="E146" t="s">
+        <v>36</v>
+      </c>
+      <c r="F146" s="1">
+        <v>46093</v>
+      </c>
+      <c r="G146" t="s">
+        <v>446</v>
+      </c>
+      <c r="H146" t="s">
+        <v>447</v>
+      </c>
+      <c r="I146" t="s">
+        <v>448</v>
+      </c>
+      <c r="J146">
+        <v>1</v>
+      </c>
+      <c r="K146">
+        <v>22.04</v>
+      </c>
+      <c r="L146">
+        <v>22.04</v>
+      </c>
+      <c r="M146" t="s">
+        <v>22</v>
+      </c>
+      <c r="N146" t="s">
+        <v>23</v>
+      </c>
+      <c r="O146" s="1">
+        <v>46092</v>
+      </c>
+      <c r="P146" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>24</v>
+      </c>
+      <c r="R146" t="s">
+        <v>41</v>
+      </c>
+      <c r="S146" t="s">
+        <v>25</v>
+      </c>
+      <c r="T146" t="s">
+        <v>42</v>
+      </c>
+      <c r="U146" t="s">
+        <v>43</v>
+      </c>
+      <c r="V146" t="s">
+        <v>44</v>
+      </c>
+      <c r="W146" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="147" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>450</v>
+      </c>
+      <c r="B147" t="s">
+        <v>451</v>
+      </c>
+      <c r="C147" t="s">
+        <v>34</v>
+      </c>
+      <c r="D147" t="s">
+        <v>35</v>
+      </c>
+      <c r="E147" t="s">
+        <v>36</v>
+      </c>
+      <c r="F147" s="1">
+        <v>46094</v>
+      </c>
+      <c r="G147" t="s">
+        <v>452</v>
+      </c>
+      <c r="H147" t="s">
+        <v>453</v>
+      </c>
+      <c r="I147" t="s">
+        <v>454</v>
+      </c>
+      <c r="J147">
+        <v>3</v>
+      </c>
+      <c r="K147">
+        <v>15.5</v>
+      </c>
+      <c r="L147">
+        <v>46.5</v>
+      </c>
+      <c r="M147" t="s">
+        <v>22</v>
+      </c>
+      <c r="N147" t="s">
+        <v>23</v>
+      </c>
+      <c r="O147" s="1">
+        <v>46094</v>
+      </c>
+      <c r="P147" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>24</v>
+      </c>
+      <c r="R147" t="s">
+        <v>41</v>
+      </c>
+      <c r="S147" t="s">
+        <v>25</v>
+      </c>
+      <c r="T147" t="s">
+        <v>42</v>
+      </c>
+      <c r="U147" t="s">
+        <v>43</v>
+      </c>
+      <c r="V147" t="s">
+        <v>44</v>
+      </c>
+      <c r="W147" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="148" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>450</v>
+      </c>
+      <c r="B148" t="s">
+        <v>451</v>
+      </c>
+      <c r="C148" t="s">
+        <v>34</v>
+      </c>
+      <c r="D148" t="s">
+        <v>35</v>
+      </c>
+      <c r="E148" t="s">
+        <v>36</v>
+      </c>
+      <c r="F148" s="1">
+        <v>46094</v>
+      </c>
+      <c r="G148" t="s">
+        <v>455</v>
+      </c>
+      <c r="H148" t="s">
+        <v>456</v>
+      </c>
+      <c r="I148" t="s">
+        <v>457</v>
+      </c>
+      <c r="J148">
+        <v>12</v>
+      </c>
+      <c r="K148">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="L148">
+        <v>98.4</v>
+      </c>
+      <c r="M148" t="s">
+        <v>22</v>
+      </c>
+      <c r="N148" t="s">
+        <v>23</v>
+      </c>
+      <c r="O148" s="1">
+        <v>46094</v>
+      </c>
+      <c r="P148" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>24</v>
+      </c>
+      <c r="R148" t="s">
+        <v>41</v>
+      </c>
+      <c r="S148" t="s">
+        <v>25</v>
+      </c>
+      <c r="T148" t="s">
+        <v>42</v>
+      </c>
+      <c r="U148" t="s">
+        <v>43</v>
+      </c>
+      <c r="V148" t="s">
+        <v>44</v>
+      </c>
+      <c r="W148" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="149" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>450</v>
+      </c>
+      <c r="B149" t="s">
+        <v>451</v>
+      </c>
+      <c r="C149" t="s">
+        <v>34</v>
+      </c>
+      <c r="D149" t="s">
+        <v>35</v>
+      </c>
+      <c r="E149" t="s">
+        <v>36</v>
+      </c>
+      <c r="F149" s="1">
+        <v>46094</v>
+      </c>
+      <c r="G149" t="s">
+        <v>153</v>
+      </c>
+      <c r="H149" t="s">
+        <v>154</v>
+      </c>
+      <c r="I149" t="s">
+        <v>155</v>
+      </c>
+      <c r="J149">
+        <v>12</v>
+      </c>
+      <c r="K149">
+        <v>15.26</v>
+      </c>
+      <c r="L149">
+        <v>183.12</v>
+      </c>
+      <c r="M149" t="s">
+        <v>22</v>
+      </c>
+      <c r="N149" t="s">
+        <v>23</v>
+      </c>
+      <c r="O149" s="1">
+        <v>46094</v>
+      </c>
+      <c r="P149" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>24</v>
+      </c>
+      <c r="R149" t="s">
+        <v>41</v>
+      </c>
+      <c r="S149" t="s">
+        <v>25</v>
+      </c>
+      <c r="T149" t="s">
+        <v>42</v>
+      </c>
+      <c r="U149" t="s">
+        <v>43</v>
+      </c>
+      <c r="V149" t="s">
+        <v>44</v>
+      </c>
+      <c r="W149" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="150" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>458</v>
+      </c>
+      <c r="B150" t="s">
+        <v>459</v>
+      </c>
+      <c r="C150" t="s">
+        <v>34</v>
+      </c>
+      <c r="D150" t="s">
+        <v>35</v>
+      </c>
+      <c r="E150" t="s">
+        <v>36</v>
+      </c>
+      <c r="F150" s="1">
+        <v>46098</v>
+      </c>
+      <c r="G150" t="s">
+        <v>460</v>
+      </c>
+      <c r="H150" t="s">
+        <v>461</v>
+      </c>
+      <c r="I150" t="s">
+        <v>462</v>
+      </c>
+      <c r="J150">
+        <v>1</v>
+      </c>
+      <c r="K150">
+        <v>13.12</v>
+      </c>
+      <c r="L150">
+        <v>13.12</v>
+      </c>
+      <c r="M150" t="s">
+        <v>22</v>
+      </c>
+      <c r="N150" t="s">
+        <v>23</v>
+      </c>
+      <c r="O150" s="1">
+        <v>46097</v>
+      </c>
+      <c r="P150" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q150" t="s">
+        <v>24</v>
+      </c>
+      <c r="R150" t="s">
+        <v>41</v>
+      </c>
+      <c r="S150" t="s">
+        <v>25</v>
+      </c>
+      <c r="T150" t="s">
+        <v>42</v>
+      </c>
+      <c r="U150" t="s">
+        <v>43</v>
+      </c>
+      <c r="V150" t="s">
+        <v>44</v>
+      </c>
+      <c r="W150" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="151" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>458</v>
+      </c>
+      <c r="B151" t="s">
+        <v>459</v>
+      </c>
+      <c r="C151" t="s">
+        <v>34</v>
+      </c>
+      <c r="D151" t="s">
+        <v>35</v>
+      </c>
+      <c r="E151" t="s">
+        <v>36</v>
+      </c>
+      <c r="F151" s="1">
+        <v>46098</v>
+      </c>
+      <c r="G151" t="s">
+        <v>153</v>
+      </c>
+      <c r="H151" t="s">
+        <v>154</v>
+      </c>
+      <c r="I151" t="s">
+        <v>155</v>
+      </c>
+      <c r="J151">
+        <v>12</v>
+      </c>
+      <c r="K151">
+        <v>15.26</v>
+      </c>
+      <c r="L151">
+        <v>183.12</v>
+      </c>
+      <c r="M151" t="s">
+        <v>22</v>
+      </c>
+      <c r="N151" t="s">
+        <v>23</v>
+      </c>
+      <c r="O151" s="1">
+        <v>46097</v>
+      </c>
+      <c r="P151" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>24</v>
+      </c>
+      <c r="R151" t="s">
+        <v>41</v>
+      </c>
+      <c r="S151" t="s">
+        <v>25</v>
+      </c>
+      <c r="T151" t="s">
+        <v>42</v>
+      </c>
+      <c r="U151" t="s">
+        <v>43</v>
+      </c>
+      <c r="V151" t="s">
+        <v>44</v>
+      </c>
+      <c r="W151" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="152" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>463</v>
+      </c>
+      <c r="B152" t="s">
+        <v>464</v>
+      </c>
+      <c r="C152" t="s">
+        <v>34</v>
+      </c>
+      <c r="D152" t="s">
+        <v>35</v>
+      </c>
+      <c r="E152" t="s">
+        <v>36</v>
+      </c>
+      <c r="F152" s="1">
+        <v>46098</v>
+      </c>
+      <c r="G152" t="s">
+        <v>465</v>
+      </c>
+      <c r="H152" t="s">
+        <v>466</v>
+      </c>
+      <c r="I152" t="s">
+        <v>467</v>
+      </c>
+      <c r="J152">
+        <v>2</v>
+      </c>
+      <c r="K152">
+        <v>9.2899999999999991</v>
+      </c>
+      <c r="L152">
+        <v>18.579999999999998</v>
+      </c>
+      <c r="M152" t="s">
+        <v>22</v>
+      </c>
+      <c r="N152" t="s">
+        <v>23</v>
+      </c>
+      <c r="O152" s="1">
+        <v>46098</v>
+      </c>
+      <c r="P152" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>24</v>
+      </c>
+      <c r="R152" t="s">
+        <v>41</v>
+      </c>
+      <c r="S152" t="s">
+        <v>25</v>
+      </c>
+      <c r="T152" t="s">
+        <v>42</v>
+      </c>
+      <c r="U152" t="s">
+        <v>43</v>
+      </c>
+      <c r="V152" t="s">
+        <v>44</v>
+      </c>
+      <c r="W152" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="153" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>463</v>
+      </c>
+      <c r="B153" t="s">
+        <v>464</v>
+      </c>
+      <c r="C153" t="s">
+        <v>34</v>
+      </c>
+      <c r="D153" t="s">
+        <v>35</v>
+      </c>
+      <c r="E153" t="s">
+        <v>36</v>
+      </c>
+      <c r="F153" s="1">
+        <v>46098</v>
+      </c>
+      <c r="G153" t="s">
+        <v>329</v>
+      </c>
+      <c r="H153" t="s">
+        <v>330</v>
+      </c>
+      <c r="I153" t="s">
+        <v>331</v>
+      </c>
+      <c r="J153">
+        <v>1</v>
+      </c>
+      <c r="K153">
+        <v>11.19</v>
+      </c>
+      <c r="L153">
+        <v>11.19</v>
+      </c>
+      <c r="M153" t="s">
+        <v>22</v>
+      </c>
+      <c r="N153" t="s">
+        <v>23</v>
+      </c>
+      <c r="O153" s="1">
+        <v>46098</v>
+      </c>
+      <c r="P153" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>24</v>
+      </c>
+      <c r="R153" t="s">
+        <v>41</v>
+      </c>
+      <c r="S153" t="s">
+        <v>25</v>
+      </c>
+      <c r="T153" t="s">
+        <v>42</v>
+      </c>
+      <c r="U153" t="s">
+        <v>43</v>
+      </c>
+      <c r="V153" t="s">
+        <v>44</v>
+      </c>
+      <c r="W153" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="154" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>463</v>
+      </c>
+      <c r="B154" t="s">
+        <v>464</v>
+      </c>
+      <c r="C154" t="s">
+        <v>34</v>
+      </c>
+      <c r="D154" t="s">
+        <v>35</v>
+      </c>
+      <c r="E154" t="s">
+        <v>36</v>
+      </c>
+      <c r="F154" s="1">
+        <v>46098</v>
+      </c>
+      <c r="G154" t="s">
+        <v>468</v>
+      </c>
+      <c r="H154" t="s">
+        <v>469</v>
+      </c>
+      <c r="I154" t="s">
+        <v>470</v>
+      </c>
+      <c r="J154">
+        <v>1</v>
+      </c>
+      <c r="K154">
+        <v>7.98</v>
+      </c>
+      <c r="L154">
+        <v>7.98</v>
+      </c>
+      <c r="M154" t="s">
+        <v>22</v>
+      </c>
+      <c r="N154" t="s">
+        <v>23</v>
+      </c>
+      <c r="O154" s="1">
+        <v>46098</v>
+      </c>
+      <c r="P154" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>24</v>
+      </c>
+      <c r="R154" t="s">
+        <v>41</v>
+      </c>
+      <c r="S154" t="s">
+        <v>25</v>
+      </c>
+      <c r="T154" t="s">
+        <v>42</v>
+      </c>
+      <c r="U154" t="s">
+        <v>43</v>
+      </c>
+      <c r="V154" t="s">
+        <v>44</v>
+      </c>
+      <c r="W154" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="155" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>463</v>
+      </c>
+      <c r="B155" t="s">
+        <v>464</v>
+      </c>
+      <c r="C155" t="s">
+        <v>34</v>
+      </c>
+      <c r="D155" t="s">
+        <v>35</v>
+      </c>
+      <c r="E155" t="s">
+        <v>36</v>
+      </c>
+      <c r="F155" s="1">
+        <v>46098</v>
+      </c>
+      <c r="G155" t="s">
+        <v>245</v>
+      </c>
+      <c r="H155" t="s">
+        <v>246</v>
+      </c>
+      <c r="I155" t="s">
+        <v>247</v>
+      </c>
+      <c r="J155">
+        <v>1</v>
+      </c>
+      <c r="K155">
+        <v>41.4</v>
+      </c>
+      <c r="L155">
+        <v>41.4</v>
+      </c>
+      <c r="M155" t="s">
+        <v>22</v>
+      </c>
+      <c r="N155" t="s">
+        <v>23</v>
+      </c>
+      <c r="O155" s="1">
+        <v>46098</v>
+      </c>
+      <c r="P155" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q155" t="s">
+        <v>24</v>
+      </c>
+      <c r="R155" t="s">
+        <v>41</v>
+      </c>
+      <c r="S155" t="s">
+        <v>25</v>
+      </c>
+      <c r="T155" t="s">
+        <v>42</v>
+      </c>
+      <c r="U155" t="s">
+        <v>43</v>
+      </c>
+      <c r="V155" t="s">
+        <v>44</v>
+      </c>
+      <c r="W155" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="156" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>463</v>
+      </c>
+      <c r="B156" t="s">
+        <v>464</v>
+      </c>
+      <c r="C156" t="s">
+        <v>34</v>
+      </c>
+      <c r="D156" t="s">
+        <v>35</v>
+      </c>
+      <c r="E156" t="s">
+        <v>36</v>
+      </c>
+      <c r="F156" s="1">
+        <v>46098</v>
+      </c>
+      <c r="G156" t="s">
+        <v>291</v>
+      </c>
+      <c r="H156" t="s">
+        <v>292</v>
+      </c>
+      <c r="I156" t="s">
+        <v>293</v>
+      </c>
+      <c r="J156">
+        <v>2</v>
+      </c>
+      <c r="K156">
+        <v>11.33</v>
+      </c>
+      <c r="L156">
+        <v>22.66</v>
+      </c>
+      <c r="M156" t="s">
+        <v>22</v>
+      </c>
+      <c r="N156" t="s">
+        <v>23</v>
+      </c>
+      <c r="O156" s="1">
+        <v>46098</v>
+      </c>
+      <c r="P156" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q156" t="s">
+        <v>24</v>
+      </c>
+      <c r="R156" t="s">
+        <v>41</v>
+      </c>
+      <c r="S156" t="s">
+        <v>25</v>
+      </c>
+      <c r="T156" t="s">
+        <v>42</v>
+      </c>
+      <c r="U156" t="s">
+        <v>43</v>
+      </c>
+      <c r="V156" t="s">
+        <v>44</v>
+      </c>
+      <c r="W156" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="157" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>471</v>
+      </c>
+      <c r="B157" t="s">
+        <v>472</v>
+      </c>
+      <c r="C157" t="s">
+        <v>34</v>
+      </c>
+      <c r="D157" t="s">
+        <v>35</v>
+      </c>
+      <c r="E157" t="s">
+        <v>36</v>
+      </c>
+      <c r="F157" s="1">
+        <v>46105</v>
+      </c>
+      <c r="G157" t="s">
+        <v>236</v>
+      </c>
+      <c r="H157" t="s">
+        <v>237</v>
+      </c>
+      <c r="I157" t="s">
+        <v>238</v>
+      </c>
+      <c r="J157">
+        <v>2</v>
+      </c>
+      <c r="K157">
+        <v>13.67</v>
+      </c>
+      <c r="L157">
+        <v>27.34</v>
+      </c>
+      <c r="M157" t="s">
+        <v>22</v>
+      </c>
+      <c r="N157" t="s">
+        <v>23</v>
+      </c>
+      <c r="O157" s="1">
+        <v>46104</v>
+      </c>
+      <c r="P157" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q157" t="s">
+        <v>24</v>
+      </c>
+      <c r="R157" t="s">
+        <v>41</v>
+      </c>
+      <c r="S157" t="s">
+        <v>25</v>
+      </c>
+      <c r="T157" t="s">
+        <v>42</v>
+      </c>
+      <c r="U157" t="s">
+        <v>43</v>
+      </c>
+      <c r="V157" t="s">
+        <v>44</v>
+      </c>
+      <c r="W157" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="158" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>473</v>
+      </c>
+      <c r="B158" t="s">
+        <v>474</v>
+      </c>
+      <c r="C158" t="s">
+        <v>34</v>
+      </c>
+      <c r="D158" t="s">
+        <v>35</v>
+      </c>
+      <c r="E158" t="s">
+        <v>36</v>
+      </c>
+      <c r="F158" s="1">
+        <v>46108</v>
+      </c>
+      <c r="G158" t="s">
+        <v>381</v>
+      </c>
+      <c r="H158" t="s">
+        <v>382</v>
+      </c>
+      <c r="I158" t="s">
+        <v>383</v>
+      </c>
+      <c r="J158">
+        <v>1</v>
+      </c>
+      <c r="K158">
+        <v>21.6</v>
+      </c>
+      <c r="L158">
+        <v>21.6</v>
+      </c>
+      <c r="M158" t="s">
+        <v>22</v>
+      </c>
+      <c r="N158" t="s">
+        <v>23</v>
+      </c>
+      <c r="O158" s="1">
+        <v>46108</v>
+      </c>
+      <c r="P158" t="s">
+        <v>475</v>
+      </c>
+      <c r="Q158" t="s">
+        <v>24</v>
+      </c>
+      <c r="R158" t="s">
+        <v>41</v>
+      </c>
+      <c r="S158" t="s">
+        <v>25</v>
+      </c>
+      <c r="T158" t="s">
+        <v>42</v>
+      </c>
+      <c r="U158" t="s">
+        <v>43</v>
+      </c>
+      <c r="V158" t="s">
+        <v>44</v>
+      </c>
+      <c r="W158" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="159" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>473</v>
+      </c>
+      <c r="B159" t="s">
+        <v>474</v>
+      </c>
+      <c r="C159" t="s">
+        <v>34</v>
+      </c>
+      <c r="D159" t="s">
+        <v>35</v>
+      </c>
+      <c r="E159" t="s">
+        <v>36</v>
+      </c>
+      <c r="F159" s="1">
+        <v>46108</v>
+      </c>
+      <c r="G159" t="s">
+        <v>476</v>
+      </c>
+      <c r="H159" t="s">
+        <v>477</v>
+      </c>
+      <c r="I159" t="s">
+        <v>478</v>
+      </c>
+      <c r="J159">
+        <v>1</v>
+      </c>
+      <c r="K159">
+        <v>10.46</v>
+      </c>
+      <c r="L159">
+        <v>10.46</v>
+      </c>
+      <c r="M159" t="s">
+        <v>22</v>
+      </c>
+      <c r="N159" t="s">
+        <v>23</v>
+      </c>
+      <c r="O159" s="1">
+        <v>46108</v>
+      </c>
+      <c r="P159" t="s">
+        <v>475</v>
+      </c>
+      <c r="Q159" t="s">
+        <v>24</v>
+      </c>
+      <c r="R159" t="s">
+        <v>41</v>
+      </c>
+      <c r="S159" t="s">
+        <v>25</v>
+      </c>
+      <c r="T159" t="s">
+        <v>42</v>
+      </c>
+      <c r="U159" t="s">
+        <v>43</v>
+      </c>
+      <c r="V159" t="s">
+        <v>44</v>
+      </c>
+      <c r="W159" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="160" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>479</v>
+      </c>
+      <c r="B160" t="s">
+        <v>480</v>
+      </c>
+      <c r="C160" t="s">
+        <v>34</v>
+      </c>
+      <c r="D160" t="s">
+        <v>35</v>
+      </c>
+      <c r="E160" t="s">
+        <v>36</v>
+      </c>
+      <c r="F160" s="1">
+        <v>46108</v>
+      </c>
+      <c r="G160" t="s">
+        <v>185</v>
+      </c>
+      <c r="H160" t="s">
+        <v>186</v>
+      </c>
+      <c r="I160" t="s">
+        <v>187</v>
+      </c>
+      <c r="J160">
+        <v>1</v>
+      </c>
+      <c r="K160">
+        <v>7.49</v>
+      </c>
+      <c r="L160">
+        <v>7.49</v>
+      </c>
+      <c r="M160" t="s">
+        <v>22</v>
+      </c>
+      <c r="N160" t="s">
+        <v>23</v>
+      </c>
+      <c r="O160" s="1">
+        <v>46108</v>
+      </c>
+      <c r="P160" t="s">
+        <v>481</v>
+      </c>
+      <c r="Q160" t="s">
+        <v>24</v>
+      </c>
+      <c r="R160" t="s">
+        <v>41</v>
+      </c>
+      <c r="S160" t="s">
+        <v>25</v>
+      </c>
+      <c r="T160" t="s">
+        <v>42</v>
+      </c>
+      <c r="U160" t="s">
+        <v>43</v>
+      </c>
+      <c r="V160" t="s">
+        <v>44</v>
+      </c>
+      <c r="W160" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="161" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>482</v>
+      </c>
+      <c r="B161" t="s">
+        <v>483</v>
+      </c>
+      <c r="C161" t="s">
+        <v>484</v>
+      </c>
+      <c r="D161" t="s">
+        <v>484</v>
+      </c>
+      <c r="E161" t="s">
+        <v>485</v>
+      </c>
+      <c r="F161" s="1">
+        <v>46086</v>
+      </c>
+      <c r="G161" t="s">
+        <v>486</v>
+      </c>
+      <c r="H161" t="s">
+        <v>487</v>
+      </c>
+      <c r="I161" t="s">
+        <v>488</v>
+      </c>
+      <c r="J161">
+        <v>1</v>
+      </c>
+      <c r="K161">
+        <v>576</v>
+      </c>
+      <c r="L161">
+        <v>576</v>
+      </c>
+      <c r="M161" t="s">
+        <v>22</v>
+      </c>
+      <c r="N161" t="s">
+        <v>23</v>
+      </c>
+      <c r="O161" s="1">
+        <v>46085</v>
+      </c>
+      <c r="P161" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q161" t="s">
+        <v>24</v>
+      </c>
+      <c r="R161" t="s">
+        <v>490</v>
+      </c>
+      <c r="S161" t="s">
+        <v>25</v>
+      </c>
+      <c r="T161" t="s">
+        <v>42</v>
+      </c>
+      <c r="U161" t="s">
+        <v>43</v>
+      </c>
+      <c r="V161" t="s">
+        <v>491</v>
+      </c>
+      <c r="W161" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="162" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>492</v>
+      </c>
+      <c r="B162" t="s">
+        <v>493</v>
+      </c>
+      <c r="C162" t="s">
+        <v>484</v>
+      </c>
+      <c r="D162" t="s">
+        <v>484</v>
+      </c>
+      <c r="E162" t="s">
+        <v>485</v>
+      </c>
+      <c r="F162" s="1">
+        <v>46086</v>
+      </c>
+      <c r="G162" t="s">
+        <v>494</v>
+      </c>
+      <c r="H162" t="s">
+        <v>495</v>
+      </c>
+      <c r="I162" t="s">
+        <v>496</v>
+      </c>
+      <c r="J162">
+        <v>1</v>
+      </c>
+      <c r="K162">
+        <v>0</v>
+      </c>
+      <c r="L162">
+        <v>0</v>
+      </c>
+      <c r="M162" t="s">
+        <v>22</v>
+      </c>
+      <c r="N162" t="s">
+        <v>23</v>
+      </c>
+      <c r="O162" s="1">
+        <v>46086</v>
+      </c>
+      <c r="P162" t="s">
+        <v>497</v>
+      </c>
+      <c r="Q162" t="s">
+        <v>24</v>
+      </c>
+      <c r="R162" t="s">
+        <v>490</v>
+      </c>
+      <c r="S162" t="s">
+        <v>25</v>
+      </c>
+      <c r="T162" t="s">
+        <v>42</v>
+      </c>
+      <c r="U162" t="s">
+        <v>43</v>
+      </c>
+      <c r="V162" t="s">
+        <v>491</v>
+      </c>
+      <c r="W162" t="s">
+        <v>334</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:V96" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8303,9 +13481,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8447,19 +13628,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29EFC88C-03CF-46BD-8E1D-A1283F743150}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CADD239-2EA5-4885-881F-E6F2DFE88A8A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8483,9 +13660,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CADD239-2EA5-4885-881F-E6F2DFE88A8A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29EFC88C-03CF-46BD-8E1D-A1283F743150}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>